--- a/app/nsa_sa/DB.xlsx
+++ b/app/nsa_sa/DB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\stool\airtel\nsa_sa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aj_mac/Documents/Atel/server/code/app/nsa_sa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBF8A6B-DFE4-4D9C-8E14-4324431B1F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEE3297-86BB-744B-9EA0-6689D36E22D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17208" yWindow="4296" windowWidth="17316" windowHeight="10668" activeTab="5" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15960" activeTab="5" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
   </bookViews>
   <sheets>
     <sheet name="TermPointToAmf" sheetId="2" r:id="rId1"/>
@@ -37,15 +37,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="510">
   <si>
     <t>5qi1</t>
   </si>
@@ -1566,13 +1563,22 @@
   </si>
   <si>
     <t>Not Implemented</t>
+  </si>
+  <si>
+    <t>["NG"]</t>
+  </si>
+  <si>
+    <t>["XN"]</t>
+  </si>
+  <si>
+    <t>[{"sd":  "1", "sst":  "1"}]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1603,6 +1609,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1673,7 +1686,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1684,13 +1697,10 @@
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1709,9 +1719,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1749,7 +1759,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1855,7 +1865,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1997,7 +2007,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2006,18 +2016,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247B63BC-5D3A-4B06-850D-E1325BAD072A}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>369</v>
       </c>
@@ -2046,7 +2056,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -2075,7 +2085,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
@@ -2104,7 +2114,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>40</v>
       </c>
@@ -2133,7 +2143,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
@@ -2162,7 +2172,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>40</v>
       </c>
@@ -2191,7 +2201,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>40</v>
       </c>
@@ -2220,7 +2230,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>455</v>
       </c>
@@ -2249,7 +2259,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>455</v>
       </c>
@@ -2287,31 +2297,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033B3FD-ABCD-4751-AD44-826E517C5D04}">
   <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultColWidth="48.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="48.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="55.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="63.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="62.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="43.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="49.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="45.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="55.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="63.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="62.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="45.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>369</v>
       </c>
@@ -2373,7 +2383,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -2435,7 +2445,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
@@ -2497,7 +2507,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>24</v>
       </c>
@@ -2559,7 +2569,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
@@ -2621,7 +2631,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -2683,7 +2693,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
@@ -2745,7 +2755,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>40</v>
       </c>
@@ -2807,7 +2817,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>40</v>
       </c>
@@ -2869,7 +2879,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
@@ -2931,7 +2941,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
@@ -2993,7 +3003,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
@@ -3055,7 +3065,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
@@ -3117,7 +3127,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
@@ -3179,7 +3189,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>455</v>
       </c>
@@ -3241,7 +3251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>455</v>
       </c>
@@ -3303,7 +3313,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>455</v>
       </c>
@@ -3365,7 +3375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>455</v>
       </c>
@@ -3427,7 +3437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>455</v>
       </c>
@@ -3489,7 +3499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>455</v>
       </c>
@@ -3551,7 +3561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>455</v>
       </c>
@@ -3613,7 +3623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>455</v>
       </c>
@@ -3675,7 +3685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>455</v>
       </c>
@@ -3737,7 +3747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3759,7 +3769,7 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3781,7 +3791,7 @@
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3803,7 +3813,7 @@
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3825,7 +3835,7 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3847,7 +3857,7 @@
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3869,7 +3879,7 @@
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3891,7 +3901,7 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3913,7 +3923,7 @@
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3935,7 +3945,7 @@
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3957,7 +3967,7 @@
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3979,7 +3989,7 @@
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -4001,7 +4011,7 @@
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -4023,7 +4033,7 @@
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4045,7 +4055,7 @@
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4067,7 +4077,7 @@
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4089,7 +4099,7 @@
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4120,26 +4130,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79F24CE-09F9-45C1-9181-E9678DF90F16}">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="39.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="39.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="40" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>369</v>
       </c>
@@ -4186,7 +4196,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>439</v>
       </c>
@@ -4233,7 +4243,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>439</v>
       </c>
@@ -4280,7 +4290,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>439</v>
       </c>
@@ -4327,7 +4337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>439</v>
       </c>
@@ -4374,7 +4384,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>439</v>
       </c>
@@ -4421,7 +4431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>439</v>
       </c>
@@ -4468,7 +4478,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>439</v>
       </c>
@@ -4515,7 +4525,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>439</v>
       </c>
@@ -4562,7 +4572,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>439</v>
       </c>
@@ -4618,19 +4628,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D5106C-E246-4D86-AA70-24537FEFA393}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>369</v>
       </c>
@@ -4656,7 +4666,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>439</v>
       </c>
@@ -4682,7 +4692,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>439</v>
       </c>
@@ -4708,7 +4718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>439</v>
       </c>
@@ -4734,7 +4744,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>439</v>
       </c>
@@ -4760,7 +4770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>439</v>
       </c>
@@ -4786,7 +4796,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>439</v>
       </c>
@@ -4812,7 +4822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>439</v>
       </c>
@@ -4838,7 +4848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>439</v>
       </c>
@@ -4864,7 +4874,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>439</v>
       </c>
@@ -4898,26 +4908,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20CE4695-3474-4204-BA59-43EE895CC990}">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="56" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>369</v>
       </c>
@@ -4964,7 +4974,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>439</v>
       </c>
@@ -5011,7 +5021,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>439</v>
       </c>
@@ -5058,7 +5068,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>439</v>
       </c>
@@ -5105,7 +5115,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>439</v>
       </c>
@@ -5152,7 +5162,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>439</v>
       </c>
@@ -5199,7 +5209,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>439</v>
       </c>
@@ -5246,7 +5256,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>439</v>
       </c>
@@ -5293,7 +5303,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>439</v>
       </c>
@@ -5340,7 +5350,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>439</v>
       </c>
@@ -5396,22 +5406,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04129BFA-1C57-4A9F-9E8B-6ECAA0BFBBBF}">
   <dimension ref="A1:H269"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.1796875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="46.81640625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="24.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.81640625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="6" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.81640625" style="10" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="7"/>
+    <col min="1" max="1" width="7.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="24.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.83203125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="6" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53.83203125" style="8" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>369</v>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>474</v>
@@ -5435,359 +5445,359 @@
         <v>447</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C2" s="11" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="F2" s="11" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G3" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="E3" s="12" t="s">
+      <c r="H3" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="F3" s="11" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="E4" s="12" t="s">
+      <c r="G4" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="F4" s="11" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="G5" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="11" t="s">
+      <c r="D6" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G6" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="H6" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="11" t="s">
+      <c r="D7" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G7" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="11" t="s">
+      <c r="H7" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G8" s="9"/>
+      <c r="H8" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="H7" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="H14" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>480</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="F8" s="11" t="s">
+      <c r="B15" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>481</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>482</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>483</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>485</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="11" t="s">
+      <c r="G15" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" s="12" t="s">
+      <c r="H15" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>443</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>439</v>
       </c>
@@ -5800,18 +5810,18 @@
       <c r="D16" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="3" t="s">
         <v>171</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>439</v>
       </c>
@@ -5824,18 +5834,18 @@
       <c r="D17" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H17" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>439</v>
       </c>
@@ -5848,18 +5858,18 @@
       <c r="D18" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="3" t="s">
         <v>171</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="3"/>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>439</v>
       </c>
@@ -5872,18 +5882,18 @@
       <c r="D19" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="3"/>
-      <c r="H19" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H19" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>439</v>
       </c>
@@ -5896,18 +5906,18 @@
       <c r="D20" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>439</v>
       </c>
@@ -5920,18 +5930,18 @@
       <c r="D21" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="3" t="s">
         <v>398</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="3" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>439</v>
       </c>
@@ -5944,18 +5954,18 @@
       <c r="D22" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="3"/>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>439</v>
       </c>
@@ -5968,18 +5978,18 @@
       <c r="D23" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>439</v>
       </c>
@@ -5992,18 +6002,18 @@
       <c r="D24" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="3" t="s">
         <v>200</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="3" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>439</v>
       </c>
@@ -6016,18 +6026,18 @@
       <c r="D25" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G25" s="3"/>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>439</v>
       </c>
@@ -6040,18 +6050,18 @@
       <c r="D26" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="3">
         <v>34</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="3"/>
-      <c r="H26" s="8">
+      <c r="H26" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>439</v>
       </c>
@@ -6064,18 +6074,18 @@
       <c r="D27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="3">
         <v>34</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="3"/>
-      <c r="H27" s="8">
+      <c r="H27" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>439</v>
       </c>
@@ -6088,18 +6098,18 @@
       <c r="D28" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="3">
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="3"/>
-      <c r="H28" s="8">
+      <c r="H28" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>439</v>
       </c>
@@ -6112,18 +6122,18 @@
       <c r="D29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="3">
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="3"/>
-      <c r="H29" s="8">
+      <c r="H29" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>439</v>
       </c>
@@ -6136,18 +6146,18 @@
       <c r="D30" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="3">
         <v>46</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="3"/>
-      <c r="H30" s="8">
+      <c r="H30" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>439</v>
       </c>
@@ -6160,18 +6170,18 @@
       <c r="D31" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="3">
         <v>32</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="3"/>
-      <c r="H31" s="8">
+      <c r="H31" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>439</v>
       </c>
@@ -6184,18 +6194,18 @@
       <c r="D32" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="3">
         <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="3"/>
-      <c r="H32" s="8">
+      <c r="H32" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>439</v>
       </c>
@@ -6208,18 +6218,18 @@
       <c r="D33" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="3">
         <v>30</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="3"/>
-      <c r="H33" s="8">
+      <c r="H33" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>439</v>
       </c>
@@ -6232,18 +6242,18 @@
       <c r="D34" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="3">
         <v>26</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="3"/>
-      <c r="H34" s="8">
+      <c r="H34" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>439</v>
       </c>
@@ -6256,18 +6266,18 @@
       <c r="D35" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="3" t="s">
         <v>159</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G35" s="3"/>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>439</v>
       </c>
@@ -6280,18 +6290,18 @@
       <c r="D36" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="3" t="s">
         <v>159</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="3"/>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>439</v>
       </c>
@@ -6304,18 +6314,18 @@
       <c r="D37" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="3"/>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>439</v>
       </c>
@@ -6328,18 +6338,18 @@
       <c r="D38" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>439</v>
       </c>
@@ -6352,18 +6362,18 @@
       <c r="D39" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="3"/>
-      <c r="H39" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H39" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>439</v>
       </c>
@@ -6376,18 +6386,18 @@
       <c r="D40" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="3" t="s">
         <v>399</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>439</v>
       </c>
@@ -6400,18 +6410,18 @@
       <c r="D41" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="3" t="s">
         <v>165</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="3"/>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>439</v>
       </c>
@@ -6424,18 +6434,18 @@
       <c r="D42" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="3" t="s">
         <v>166</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="3"/>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>439</v>
       </c>
@@ -6448,18 +6458,18 @@
       <c r="D43" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G43" s="3"/>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>439</v>
       </c>
@@ -6472,18 +6482,18 @@
       <c r="D44" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="3"/>
-      <c r="H44" s="8" t="s">
+      <c r="H44" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>439</v>
       </c>
@@ -6496,18 +6506,18 @@
       <c r="D45" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G45" s="3"/>
-      <c r="H45" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H45" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>439</v>
       </c>
@@ -6520,18 +6530,18 @@
       <c r="D46" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="3" t="s">
         <v>400</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="3"/>
-      <c r="H46" s="8" t="s">
+      <c r="H46" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>439</v>
       </c>
@@ -6544,18 +6554,18 @@
       <c r="D47" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G47" s="3"/>
-      <c r="H47" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H47" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>439</v>
       </c>
@@ -6568,18 +6578,18 @@
       <c r="D48" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G48" s="3"/>
-      <c r="H48" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H48" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>439</v>
       </c>
@@ -6592,18 +6602,18 @@
       <c r="D49" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G49" s="3"/>
-      <c r="H49" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H49" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>439</v>
       </c>
@@ -6616,18 +6626,18 @@
       <c r="D50" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G50" s="3"/>
-      <c r="H50" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H50" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>439</v>
       </c>
@@ -6640,18 +6650,18 @@
       <c r="D51" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G51" s="3"/>
-      <c r="H51" s="8" t="s">
+      <c r="H51" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>439</v>
       </c>
@@ -6664,18 +6674,18 @@
       <c r="D52" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G52" s="3"/>
-      <c r="H52" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H52" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>439</v>
       </c>
@@ -6688,18 +6698,18 @@
       <c r="D53" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G53" s="3"/>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>439</v>
       </c>
@@ -6712,18 +6722,18 @@
       <c r="D54" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="3" t="s">
         <v>503</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G54" s="3"/>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>439</v>
       </c>
@@ -6736,18 +6746,18 @@
       <c r="D55" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G55" s="3"/>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>439</v>
       </c>
@@ -6760,18 +6770,18 @@
       <c r="D56" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G56" s="3"/>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>439</v>
       </c>
@@ -6784,18 +6794,18 @@
       <c r="D57" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G57" s="3"/>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>439</v>
       </c>
@@ -6808,18 +6818,18 @@
       <c r="D58" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G58" s="3"/>
-      <c r="H58" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H58" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>439</v>
       </c>
@@ -6832,18 +6842,18 @@
       <c r="D59" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G59" s="3"/>
-      <c r="H59" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H59" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>439</v>
       </c>
@@ -6856,18 +6866,18 @@
       <c r="D60" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="3" t="s">
         <v>401</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G60" s="3"/>
-      <c r="H60" s="8" t="s">
+      <c r="H60" s="3" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>439</v>
       </c>
@@ -6880,18 +6890,18 @@
       <c r="D61" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="3" t="s">
         <v>248</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G61" s="3"/>
-      <c r="H61" s="8" t="s">
+      <c r="H61" s="3" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>439</v>
       </c>
@@ -6904,18 +6914,18 @@
       <c r="D62" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="3" t="s">
         <v>402</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G62" s="3"/>
-      <c r="H62" s="8" t="s">
+      <c r="H62" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>439</v>
       </c>
@@ -6928,18 +6938,18 @@
       <c r="D63" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="3" t="s">
         <v>402</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G63" s="3"/>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>439</v>
       </c>
@@ -6952,18 +6962,18 @@
       <c r="D64" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G64" s="3"/>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>439</v>
       </c>
@@ -6976,18 +6986,18 @@
       <c r="D65" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="3" t="s">
         <v>403</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G65" s="3"/>
-      <c r="H65" s="8" t="s">
+      <c r="H65" s="3" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>439</v>
       </c>
@@ -7000,18 +7010,18 @@
       <c r="D66" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="3" t="s">
         <v>256</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G66" s="3"/>
-      <c r="H66" s="8" t="s">
+      <c r="H66" s="3" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>439</v>
       </c>
@@ -7024,18 +7034,18 @@
       <c r="D67" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="3" t="s">
         <v>258</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G67" s="3"/>
-      <c r="H67" s="8" t="s">
+      <c r="H67" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>439</v>
       </c>
@@ -7048,18 +7058,18 @@
       <c r="D68" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G68" s="3"/>
-      <c r="H68" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H68" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>439</v>
       </c>
@@ -7072,18 +7082,18 @@
       <c r="D69" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G69" s="3"/>
-      <c r="H69" s="8" t="s">
+      <c r="H69" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>439</v>
       </c>
@@ -7096,18 +7106,18 @@
       <c r="D70" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G70" s="3"/>
-      <c r="H70" s="8" t="s">
+      <c r="H70" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>439</v>
       </c>
@@ -7120,18 +7130,18 @@
       <c r="D71" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G71" s="3"/>
-      <c r="H71" s="8" t="s">
+      <c r="H71" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>439</v>
       </c>
@@ -7144,18 +7154,18 @@
       <c r="D72" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G72" s="3"/>
-      <c r="H72" s="8" t="s">
+      <c r="H72" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>439</v>
       </c>
@@ -7168,18 +7178,18 @@
       <c r="D73" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="3" t="s">
         <v>414</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G73" s="3"/>
-      <c r="H73" s="8" t="s">
+      <c r="H73" s="3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>439</v>
       </c>
@@ -7192,18 +7202,18 @@
       <c r="D74" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G74" s="3"/>
-      <c r="H74" s="8" t="s">
+      <c r="H74" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>439</v>
       </c>
@@ -7216,18 +7226,18 @@
       <c r="D75" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E75" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G75" s="3"/>
-      <c r="H75" s="8" t="s">
+      <c r="H75" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>439</v>
       </c>
@@ -7240,18 +7250,18 @@
       <c r="D76" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G76" s="3"/>
-      <c r="H76" s="8" t="s">
+      <c r="H76" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>439</v>
       </c>
@@ -7264,16 +7274,16 @@
       <c r="D77" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="E77" s="8"/>
+      <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G77" s="3"/>
-      <c r="H77" s="8" t="s">
+      <c r="H77" s="3" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>439</v>
       </c>
@@ -7286,18 +7296,18 @@
       <c r="D78" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="3" t="s">
         <v>403</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G78" s="3"/>
-      <c r="H78" s="8" t="s">
+      <c r="H78" s="3" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>439</v>
       </c>
@@ -7310,18 +7320,18 @@
       <c r="D79" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E79" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G79" s="3"/>
-      <c r="H79" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H79" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>439</v>
       </c>
@@ -7334,18 +7344,18 @@
       <c r="D80" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E80" s="8" t="s">
+      <c r="E80" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G80" s="3"/>
-      <c r="H80" s="8" t="s">
+      <c r="H80" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>439</v>
       </c>
@@ -7358,18 +7368,18 @@
       <c r="D81" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="3" t="s">
         <v>299</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G81" s="3"/>
-      <c r="H81" s="8" t="s">
+      <c r="H81" s="3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>439</v>
       </c>
@@ -7382,18 +7392,18 @@
       <c r="D82" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="3" t="s">
         <v>440</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G82" s="3"/>
-      <c r="H82" s="8" t="s">
+      <c r="H82" s="3" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>439</v>
       </c>
@@ -7406,18 +7416,18 @@
       <c r="D83" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E83" s="8" t="s">
+      <c r="E83" s="3" t="s">
         <v>304</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G83" s="3"/>
-      <c r="H83" s="8" t="s">
+      <c r="H83" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>439</v>
       </c>
@@ -7430,18 +7440,18 @@
       <c r="D84" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E84" s="3" t="s">
         <v>305</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G84" s="3"/>
-      <c r="H84" s="8" t="s">
+      <c r="H84" s="3" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>439</v>
       </c>
@@ -7454,18 +7464,18 @@
       <c r="D85" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="E85" s="8" t="s">
+      <c r="E85" s="3" t="s">
         <v>403</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G85" s="3"/>
-      <c r="H85" s="8" t="s">
+      <c r="H85" s="3" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>439</v>
       </c>
@@ -7478,18 +7488,18 @@
       <c r="D86" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G86" s="3"/>
-      <c r="H86" s="8" t="s">
+      <c r="H86" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>439</v>
       </c>
@@ -7502,18 +7512,18 @@
       <c r="D87" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E87" s="8" t="s">
+      <c r="E87" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G87" s="3"/>
-      <c r="H87" s="8" t="s">
+      <c r="H87" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>439</v>
       </c>
@@ -7526,18 +7536,18 @@
       <c r="D88" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E88" s="8" t="s">
+      <c r="E88" s="3" t="s">
         <v>297</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G88" s="3"/>
-      <c r="H88" s="8" t="s">
+      <c r="H88" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>439</v>
       </c>
@@ -7550,18 +7560,18 @@
       <c r="D89" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E89" s="8" t="s">
+      <c r="E89" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G89" s="3"/>
-      <c r="H89" s="8" t="s">
+      <c r="H89" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>439</v>
       </c>
@@ -7574,18 +7584,18 @@
       <c r="D90" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="3" t="s">
         <v>300</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G90" s="3"/>
-      <c r="H90" s="8" t="s">
+      <c r="H90" s="3" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>439</v>
       </c>
@@ -7598,18 +7608,18 @@
       <c r="D91" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="E91" s="8" t="s">
+      <c r="E91" s="3" t="s">
         <v>306</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G91" s="3"/>
-      <c r="H91" s="8" t="s">
+      <c r="H91" s="3" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>439</v>
       </c>
@@ -7622,18 +7632,18 @@
       <c r="D92" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E92" s="8" t="s">
+      <c r="E92" s="3" t="s">
         <v>307</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G92" s="3"/>
-      <c r="H92" s="8" t="s">
+      <c r="H92" s="3" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>439</v>
       </c>
@@ -7646,18 +7656,18 @@
       <c r="D93" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="E93" s="8" t="s">
+      <c r="E93" s="3" t="s">
         <v>308</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G93" s="3"/>
-      <c r="H93" s="8" t="s">
+      <c r="H93" s="3" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>439</v>
       </c>
@@ -7670,18 +7680,18 @@
       <c r="D94" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E94" s="8" t="s">
+      <c r="E94" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G94" s="3"/>
-      <c r="H94" s="8" t="s">
+      <c r="H94" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>439</v>
       </c>
@@ -7694,18 +7704,18 @@
       <c r="D95" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E95" s="8" t="s">
+      <c r="E95" s="3" t="s">
         <v>159</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G95" s="3"/>
-      <c r="H95" s="8" t="s">
+      <c r="H95" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>439</v>
       </c>
@@ -7718,18 +7728,18 @@
       <c r="D96" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="E96" s="8" t="s">
-        <v>17</v>
+      <c r="E96" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G96" s="3"/>
-      <c r="H96" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H96" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>439</v>
       </c>
@@ -7742,18 +7752,18 @@
       <c r="D97" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E97" s="8" t="s">
+      <c r="E97" s="3" t="s">
         <v>342</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G97" s="3"/>
-      <c r="H97" s="8" t="s">
+      <c r="H97" s="3" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>439</v>
       </c>
@@ -7766,18 +7776,18 @@
       <c r="D98" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" s="3" t="s">
         <v>342</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G98" s="3"/>
-      <c r="H98" s="8" t="s">
+      <c r="H98" s="3" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>439</v>
       </c>
@@ -7790,18 +7800,18 @@
       <c r="D99" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E99" s="8" t="s">
+      <c r="E99" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G99" s="3"/>
-      <c r="H99" s="8" t="s">
+      <c r="H99" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>439</v>
       </c>
@@ -7814,18 +7824,18 @@
       <c r="D100" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E100" s="3" t="s">
         <v>159</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G100" s="3"/>
-      <c r="H100" s="8" t="s">
+      <c r="H100" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>439</v>
       </c>
@@ -7838,18 +7848,18 @@
       <c r="D101" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="E101" s="8" t="s">
+      <c r="E101" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G101" s="3"/>
-      <c r="H101" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H101" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>439</v>
       </c>
@@ -7862,18 +7872,18 @@
       <c r="D102" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E102" s="8" t="s">
+      <c r="E102" s="3" t="s">
         <v>344</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G102" s="3"/>
-      <c r="H102" s="8" t="s">
+      <c r="H102" s="3" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>439</v>
       </c>
@@ -7886,18 +7896,18 @@
       <c r="D103" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E103" s="8" t="s">
+      <c r="E103" s="3" t="s">
         <v>344</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G103" s="3"/>
-      <c r="H103" s="8" t="s">
+      <c r="H103" s="3" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>439</v>
       </c>
@@ -7910,18 +7920,18 @@
       <c r="D104" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E104" s="8" t="s">
+      <c r="E104" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G104" s="3"/>
-      <c r="H104" s="8" t="s">
+      <c r="H104" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>439</v>
       </c>
@@ -7934,18 +7944,18 @@
       <c r="D105" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E105" s="8" t="s">
+      <c r="E105" s="3" t="s">
         <v>159</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G105" s="3"/>
-      <c r="H105" s="8" t="s">
+      <c r="H105" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>439</v>
       </c>
@@ -7958,18 +7968,18 @@
       <c r="D106" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G106" s="3"/>
-      <c r="H106" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H106" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>439</v>
       </c>
@@ -7982,18 +7992,18 @@
       <c r="D107" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E107" s="8" t="s">
+      <c r="E107" s="3" t="s">
         <v>346</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G107" s="3"/>
-      <c r="H107" s="8" t="s">
+      <c r="H107" s="3" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>439</v>
       </c>
@@ -8006,18 +8016,18 @@
       <c r="D108" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E108" s="8" t="s">
+      <c r="E108" s="3" t="s">
         <v>346</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G108" s="3"/>
-      <c r="H108" s="8" t="s">
+      <c r="H108" s="3" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>439</v>
       </c>
@@ -8030,18 +8040,18 @@
       <c r="D109" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="E109" s="8" t="s">
+      <c r="E109" s="3" t="s">
         <v>478</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G109" s="3"/>
-      <c r="H109" s="8" t="s">
+      <c r="H109" s="3" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>439</v>
       </c>
@@ -8054,18 +8064,18 @@
       <c r="D110" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="E110" s="8" t="s">
+      <c r="E110" s="3" t="s">
         <v>478</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G110" s="3"/>
-      <c r="H110" s="8" t="s">
+      <c r="H110" s="3" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>439</v>
       </c>
@@ -8078,18 +8088,18 @@
       <c r="D111" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="E111" s="8" t="s">
+      <c r="E111" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G111" s="3"/>
-      <c r="H111" s="8" t="s">
+      <c r="H111" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>439</v>
       </c>
@@ -8102,18 +8112,18 @@
       <c r="D112" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="E112" s="8" t="s">
+      <c r="E112" s="3" t="s">
         <v>367</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G112" s="3"/>
-      <c r="H112" s="8" t="s">
+      <c r="H112" s="3" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>439</v>
       </c>
@@ -8126,18 +8136,18 @@
       <c r="D113" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="E113" s="8" t="s">
+      <c r="E113" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G113" s="3"/>
-      <c r="H113" s="8" t="s">
+      <c r="H113" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>439</v>
       </c>
@@ -8150,18 +8160,18 @@
       <c r="D114" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="E114" s="8" t="s">
+      <c r="E114" s="3" t="s">
         <v>367</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G114" s="3"/>
-      <c r="H114" s="8" t="s">
+      <c r="H114" s="3" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>439</v>
       </c>
@@ -8174,18 +8184,18 @@
       <c r="D115" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="E115" s="8" t="s">
+      <c r="E115" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G115" s="3"/>
-      <c r="H115" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H115" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>439</v>
       </c>
@@ -8198,18 +8208,18 @@
       <c r="D116" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="E116" s="8" t="s">
+      <c r="E116" s="3" t="s">
         <v>367</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G116" s="3"/>
-      <c r="H116" s="8" t="s">
+      <c r="H116" s="3" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>439</v>
       </c>
@@ -8222,18 +8232,18 @@
       <c r="D117" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E117" s="8" t="s">
+      <c r="E117" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G117" s="3"/>
-      <c r="H117" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H117" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>439</v>
       </c>
@@ -8246,18 +8256,18 @@
       <c r="D118" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E118" s="8" t="s">
+      <c r="E118" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G118" s="3"/>
-      <c r="H118" s="8" t="s">
+      <c r="H118" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>439</v>
       </c>
@@ -8270,16 +8280,16 @@
       <c r="D119" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="E119" s="8"/>
+      <c r="E119" s="3"/>
       <c r="F119" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G119" s="3"/>
-      <c r="H119" s="8" t="s">
+      <c r="H119" s="3" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>439</v>
       </c>
@@ -8292,18 +8302,18 @@
       <c r="D120" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E120" s="8" t="s">
+      <c r="E120" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G120" s="3"/>
-      <c r="H120" s="8" t="s">
+      <c r="H120" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>439</v>
       </c>
@@ -8316,18 +8326,18 @@
       <c r="D121" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E121" s="8" t="s">
+      <c r="E121" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G121" s="3"/>
-      <c r="H121" s="8" t="s">
+      <c r="H121" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>439</v>
       </c>
@@ -8340,18 +8350,18 @@
       <c r="D122" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E122" s="8" t="s">
+      <c r="E122" s="3" t="s">
         <v>262</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G122" s="3"/>
-      <c r="H122" s="8" t="s">
+      <c r="H122" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>439</v>
       </c>
@@ -8364,18 +8374,18 @@
       <c r="D123" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E123" s="8" t="s">
+      <c r="E123" s="3" t="s">
         <v>263</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G123" s="3"/>
-      <c r="H123" s="8" t="s">
+      <c r="H123" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>439</v>
       </c>
@@ -8388,18 +8398,18 @@
       <c r="D124" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E124" s="8" t="s">
+      <c r="E124" s="3" t="s">
         <v>264</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G124" s="3"/>
-      <c r="H124" s="8" t="s">
+      <c r="H124" s="3" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>439</v>
       </c>
@@ -8412,18 +8422,18 @@
       <c r="D125" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E125" s="8" t="s">
+      <c r="E125" s="3" t="s">
         <v>181</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G125" s="3"/>
-      <c r="H125" s="8" t="s">
+      <c r="H125" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>439</v>
       </c>
@@ -8436,18 +8446,18 @@
       <c r="D126" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E126" s="8" t="s">
+      <c r="E126" s="3" t="s">
         <v>413</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G126" s="3"/>
-      <c r="H126" s="8" t="s">
+      <c r="H126" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>439</v>
       </c>
@@ -8460,18 +8470,18 @@
       <c r="D127" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E127" s="8" t="s">
+      <c r="E127" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G127" s="3"/>
-      <c r="H127" s="8" t="s">
+      <c r="H127" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>439</v>
       </c>
@@ -8484,18 +8494,18 @@
       <c r="D128" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E128" s="8" t="s">
+      <c r="E128" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G128" s="3"/>
-      <c r="H128" s="8" t="s">
+      <c r="H128" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>439</v>
       </c>
@@ -8508,18 +8518,18 @@
       <c r="D129" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E129" s="8" t="s">
+      <c r="E129" s="3" t="s">
         <v>171</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G129" s="3"/>
-      <c r="H129" s="8" t="s">
+      <c r="H129" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
         <v>439</v>
       </c>
@@ -8532,18 +8542,18 @@
       <c r="D130" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E130" s="8" t="s">
+      <c r="E130" s="3" t="s">
         <v>171</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G130" s="3"/>
-      <c r="H130" s="8" t="s">
+      <c r="H130" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>439</v>
       </c>
@@ -8556,18 +8566,18 @@
       <c r="D131" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E131" s="8" t="s">
+      <c r="E131" s="3" t="s">
         <v>183</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G131" s="3"/>
-      <c r="H131" s="8" t="s">
+      <c r="H131" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>439</v>
       </c>
@@ -8580,18 +8590,18 @@
       <c r="D132" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="E132" s="8" t="s">
+      <c r="E132" s="3" t="s">
         <v>183</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G132" s="3"/>
-      <c r="H132" s="8" t="s">
+      <c r="H132" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>439</v>
       </c>
@@ -8604,18 +8614,18 @@
       <c r="D133" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E133" s="8">
+      <c r="E133" s="3">
         <v>1500</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G133" s="3"/>
-      <c r="H133" s="8">
+      <c r="H133" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>439</v>
       </c>
@@ -8628,18 +8638,18 @@
       <c r="D134" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E134" s="8">
+      <c r="E134" s="3">
         <v>600</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G134" s="3"/>
-      <c r="H134" s="8">
+      <c r="H134" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>439</v>
       </c>
@@ -8652,18 +8662,18 @@
       <c r="D135" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E135" s="8">
+      <c r="E135" s="3">
         <v>2000</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G135" s="3"/>
-      <c r="H135" s="8">
+      <c r="H135" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>439</v>
       </c>
@@ -8676,18 +8686,18 @@
       <c r="D136" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E136" s="8">
+      <c r="E136" s="3">
         <v>3000</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G136" s="3"/>
-      <c r="H136" s="8">
+      <c r="H136" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>439</v>
       </c>
@@ -8700,18 +8710,18 @@
       <c r="D137" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E137" s="8">
+      <c r="E137" s="3">
         <v>400</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G137" s="3"/>
-      <c r="H137" s="8">
+      <c r="H137" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>439</v>
       </c>
@@ -8724,18 +8734,18 @@
       <c r="D138" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="E138" s="8" t="s">
+      <c r="E138" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G138" s="3"/>
-      <c r="H138" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H138" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
         <v>439</v>
       </c>
@@ -8748,18 +8758,18 @@
       <c r="D139" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E139" s="8" t="s">
+      <c r="E139" s="3" t="s">
         <v>404</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G139" s="3"/>
-      <c r="H139" s="8" t="s">
+      <c r="H139" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>439</v>
       </c>
@@ -8772,18 +8782,18 @@
       <c r="D140" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E140" s="8" t="s">
+      <c r="E140" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G140" s="3"/>
-      <c r="H140" s="8" t="s">
+      <c r="H140" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>439</v>
       </c>
@@ -8796,18 +8806,18 @@
       <c r="D141" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E141" s="8" t="s">
+      <c r="E141" s="3" t="s">
         <v>381</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G141" s="3"/>
-      <c r="H141" s="8" t="s">
+      <c r="H141" s="3" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
         <v>439</v>
       </c>
@@ -8820,18 +8830,18 @@
       <c r="D142" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E142" s="8" t="s">
+      <c r="E142" s="3" t="s">
         <v>380</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G142" s="3"/>
-      <c r="H142" s="8" t="s">
+      <c r="H142" s="3" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>439</v>
       </c>
@@ -8844,18 +8854,18 @@
       <c r="D143" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="E143" s="8" t="s">
+      <c r="E143" s="3" t="s">
         <v>379</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G143" s="3"/>
-      <c r="H143" s="8" t="s">
+      <c r="H143" s="3" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>439</v>
       </c>
@@ -8868,18 +8878,18 @@
       <c r="D144" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="E144" s="8" t="s">
+      <c r="E144" s="3" t="s">
         <v>378</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G144" s="3"/>
-      <c r="H144" s="8" t="s">
+      <c r="H144" s="3" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>439</v>
       </c>
@@ -8892,18 +8902,18 @@
       <c r="D145" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E145" s="8" t="s">
+      <c r="E145" s="3" t="s">
         <v>406</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G145" s="3"/>
-      <c r="H145" s="8" t="s">
+      <c r="H145" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>439</v>
       </c>
@@ -8916,18 +8926,18 @@
       <c r="D146" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="E146" s="3" t="s">
         <v>224</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G146" s="3"/>
-      <c r="H146" s="8" t="s">
+      <c r="H146" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>439</v>
       </c>
@@ -8940,18 +8950,18 @@
       <c r="D147" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E147" s="8" t="s">
+      <c r="E147" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G147" s="3"/>
-      <c r="H147" s="8" t="s">
+      <c r="H147" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
         <v>439</v>
       </c>
@@ -8964,18 +8974,18 @@
       <c r="D148" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E148" s="8" t="s">
+      <c r="E148" s="3" t="s">
         <v>405</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G148" s="3"/>
-      <c r="H148" s="8" t="s">
+      <c r="H148" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>439</v>
       </c>
@@ -8988,18 +8998,18 @@
       <c r="D149" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E149" s="8" t="s">
+      <c r="E149" s="3" t="s">
         <v>224</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G149" s="3"/>
-      <c r="H149" s="8" t="s">
+      <c r="H149" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>439</v>
       </c>
@@ -9012,18 +9022,18 @@
       <c r="D150" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E150" s="8" t="s">
+      <c r="E150" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G150" s="3"/>
-      <c r="H150" s="8" t="s">
+      <c r="H150" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>439</v>
       </c>
@@ -9036,18 +9046,18 @@
       <c r="D151" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E151" s="8" t="s">
+      <c r="E151" s="3" t="s">
         <v>406</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G151" s="3"/>
-      <c r="H151" s="8" t="s">
+      <c r="H151" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
         <v>439</v>
       </c>
@@ -9060,18 +9070,18 @@
       <c r="D152" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E152" s="8" t="s">
+      <c r="E152" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G152" s="3"/>
-      <c r="H152" s="8" t="s">
+      <c r="H152" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
         <v>439</v>
       </c>
@@ -9084,18 +9094,18 @@
       <c r="D153" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E153" s="8" t="s">
+      <c r="E153" s="3" t="s">
         <v>224</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G153" s="3"/>
-      <c r="H153" s="8" t="s">
+      <c r="H153" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
         <v>439</v>
       </c>
@@ -9108,18 +9118,18 @@
       <c r="D154" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E154" s="8" t="s">
+      <c r="E154" s="3" t="s">
         <v>405</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G154" s="3"/>
-      <c r="H154" s="8" t="s">
+      <c r="H154" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
         <v>439</v>
       </c>
@@ -9132,18 +9142,18 @@
       <c r="D155" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E155" s="8" t="s">
+      <c r="E155" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G155" s="3"/>
-      <c r="H155" s="8" t="s">
+      <c r="H155" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
         <v>439</v>
       </c>
@@ -9156,18 +9166,18 @@
       <c r="D156" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E156" s="8" t="s">
+      <c r="E156" s="3" t="s">
         <v>224</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G156" s="3"/>
-      <c r="H156" s="8" t="s">
+      <c r="H156" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
         <v>439</v>
       </c>
@@ -9180,18 +9190,18 @@
       <c r="D157" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E157" s="8" t="s">
+      <c r="E157" s="3" t="s">
         <v>406</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G157" s="3"/>
-      <c r="H157" s="8" t="s">
+      <c r="H157" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
         <v>439</v>
       </c>
@@ -9204,18 +9214,18 @@
       <c r="D158" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E158" s="8" t="s">
+      <c r="E158" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G158" s="3"/>
-      <c r="H158" s="8" t="s">
+      <c r="H158" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
         <v>439</v>
       </c>
@@ -9228,18 +9238,18 @@
       <c r="D159" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E159" s="8" t="s">
+      <c r="E159" s="3" t="s">
         <v>224</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G159" s="3"/>
-      <c r="H159" s="8" t="s">
+      <c r="H159" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
         <v>439</v>
       </c>
@@ -9252,18 +9262,18 @@
       <c r="D160" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E160" s="8" t="s">
+      <c r="E160" s="3" t="s">
         <v>405</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G160" s="3"/>
-      <c r="H160" s="8" t="s">
+      <c r="H160" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
         <v>439</v>
       </c>
@@ -9276,18 +9286,18 @@
       <c r="D161" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E161" s="8" t="s">
+      <c r="E161" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G161" s="3"/>
-      <c r="H161" s="8" t="s">
+      <c r="H161" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
         <v>439</v>
       </c>
@@ -9300,18 +9310,18 @@
       <c r="D162" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E162" s="8" t="s">
+      <c r="E162" s="3" t="s">
         <v>224</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G162" s="3"/>
-      <c r="H162" s="8" t="s">
+      <c r="H162" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
         <v>439</v>
       </c>
@@ -9324,18 +9334,18 @@
       <c r="D163" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E163" s="8" t="s">
+      <c r="E163" s="3" t="s">
         <v>227</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G163" s="3"/>
-      <c r="H163" s="8" t="s">
+      <c r="H163" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
         <v>439</v>
       </c>
@@ -9348,18 +9358,18 @@
       <c r="D164" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E164" s="8" t="s">
+      <c r="E164" s="3" t="s">
         <v>201</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G164" s="3"/>
-      <c r="H164" s="8" t="s">
+      <c r="H164" s="3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
         <v>439</v>
       </c>
@@ -9372,18 +9382,18 @@
       <c r="D165" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E165" s="8" t="s">
+      <c r="E165" s="3" t="s">
         <v>205</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G165" s="3"/>
-      <c r="H165" s="8" t="s">
+      <c r="H165" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
         <v>439</v>
       </c>
@@ -9396,18 +9406,18 @@
       <c r="D166" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E166" s="8" t="s">
+      <c r="E166" s="3" t="s">
         <v>228</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G166" s="3"/>
-      <c r="H166" s="8" t="s">
+      <c r="H166" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
         <v>439</v>
       </c>
@@ -9420,18 +9430,18 @@
       <c r="D167" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E167" s="8" t="s">
+      <c r="E167" s="3" t="s">
         <v>228</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G167" s="3"/>
-      <c r="H167" s="8" t="s">
+      <c r="H167" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
         <v>439</v>
       </c>
@@ -9444,18 +9454,18 @@
       <c r="D168" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E168" s="8" t="s">
+      <c r="E168" s="3" t="s">
         <v>229</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G168" s="3"/>
-      <c r="H168" s="8" t="s">
+      <c r="H168" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
         <v>439</v>
       </c>
@@ -9468,18 +9478,18 @@
       <c r="D169" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E169" s="8" t="s">
+      <c r="E169" s="3" t="s">
         <v>229</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G169" s="3"/>
-      <c r="H169" s="8" t="s">
+      <c r="H169" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
         <v>439</v>
       </c>
@@ -9492,18 +9502,18 @@
       <c r="D170" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E170" s="8" t="s">
+      <c r="E170" s="3" t="s">
         <v>201</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G170" s="3"/>
-      <c r="H170" s="8" t="s">
+      <c r="H170" s="3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
         <v>439</v>
       </c>
@@ -9516,18 +9526,18 @@
       <c r="D171" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E171" s="8" t="s">
+      <c r="E171" s="3" t="s">
         <v>205</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G171" s="3"/>
-      <c r="H171" s="8" t="s">
+      <c r="H171" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
         <v>439</v>
       </c>
@@ -9540,18 +9550,18 @@
       <c r="D172" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E172" s="8" t="s">
+      <c r="E172" s="3" t="s">
         <v>208</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G172" s="3"/>
-      <c r="H172" s="8" t="s">
+      <c r="H172" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
         <v>439</v>
       </c>
@@ -9564,18 +9574,18 @@
       <c r="D173" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E173" s="8" t="s">
+      <c r="E173" s="3" t="s">
         <v>209</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G173" s="3"/>
-      <c r="H173" s="8" t="s">
+      <c r="H173" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
         <v>439</v>
       </c>
@@ -9588,18 +9598,18 @@
       <c r="D174" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E174" s="8" t="s">
+      <c r="E174" s="3" t="s">
         <v>219</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G174" s="3"/>
-      <c r="H174" s="8" t="s">
+      <c r="H174" s="3" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
         <v>439</v>
       </c>
@@ -9612,18 +9622,18 @@
       <c r="D175" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E175" s="8" t="s">
+      <c r="E175" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G175" s="3"/>
-      <c r="H175" s="8" t="s">
+      <c r="H175" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
         <v>439</v>
       </c>
@@ -9636,18 +9646,18 @@
       <c r="D176" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E176" s="8" t="s">
+      <c r="E176" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G176" s="3"/>
-      <c r="H176" s="8" t="s">
+      <c r="H176" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
         <v>439</v>
       </c>
@@ -9660,18 +9670,18 @@
       <c r="D177" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E177" s="8" t="s">
+      <c r="E177" s="3" t="s">
         <v>159</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G177" s="3"/>
-      <c r="H177" s="8" t="s">
+      <c r="H177" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
         <v>439</v>
       </c>
@@ -9684,18 +9694,18 @@
       <c r="D178" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E178" s="8" t="s">
+      <c r="E178" s="3" t="s">
         <v>159</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G178" s="3"/>
-      <c r="H178" s="8" t="s">
+      <c r="H178" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
         <v>439</v>
       </c>
@@ -9708,18 +9718,18 @@
       <c r="D179" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E179" s="8" t="s">
+      <c r="E179" s="3" t="s">
         <v>201</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G179" s="3"/>
-      <c r="H179" s="8" t="s">
+      <c r="H179" s="3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
         <v>439</v>
       </c>
@@ -9732,18 +9742,18 @@
       <c r="D180" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E180" s="8" t="s">
+      <c r="E180" s="3" t="s">
         <v>205</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G180" s="3"/>
-      <c r="H180" s="8" t="s">
+      <c r="H180" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
         <v>439</v>
       </c>
@@ -9756,18 +9766,18 @@
       <c r="D181" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E181" s="8" t="s">
+      <c r="E181" s="3" t="s">
         <v>208</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G181" s="3"/>
-      <c r="H181" s="8" t="s">
+      <c r="H181" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>439</v>
       </c>
@@ -9780,18 +9790,18 @@
       <c r="D182" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E182" s="8" t="s">
+      <c r="E182" s="3" t="s">
         <v>209</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G182" s="3"/>
-      <c r="H182" s="8" t="s">
+      <c r="H182" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
         <v>439</v>
       </c>
@@ -9804,18 +9814,18 @@
       <c r="D183" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E183" s="8" t="s">
+      <c r="E183" s="3" t="s">
         <v>382</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G183" s="3"/>
-      <c r="H183" s="8" t="s">
+      <c r="H183" s="3" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
         <v>439</v>
       </c>
@@ -9828,18 +9838,18 @@
       <c r="D184" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E184" s="8" t="s">
+      <c r="E184" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G184" s="3"/>
-      <c r="H184" s="8" t="s">
+      <c r="H184" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
         <v>439</v>
       </c>
@@ -9852,18 +9862,18 @@
       <c r="D185" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E185" s="8" t="s">
+      <c r="E185" s="3" t="s">
         <v>407</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G185" s="3"/>
-      <c r="H185" s="8" t="s">
+      <c r="H185" s="3" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
         <v>439</v>
       </c>
@@ -9876,18 +9886,18 @@
       <c r="D186" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="E186" s="8" t="s">
+      <c r="E186" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G186" s="3"/>
-      <c r="H186" s="8" t="s">
+      <c r="H186" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
         <v>439</v>
       </c>
@@ -9900,18 +9910,18 @@
       <c r="D187" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="E187" s="8" t="s">
+      <c r="E187" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G187" s="3"/>
-      <c r="H187" s="8" t="s">
+      <c r="H187" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
         <v>439</v>
       </c>
@@ -9924,18 +9934,18 @@
       <c r="D188" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E188" s="8" t="s">
+      <c r="E188" s="3" t="s">
         <v>275</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G188" s="3"/>
-      <c r="H188" s="8" t="s">
+      <c r="H188" s="3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
         <v>439</v>
       </c>
@@ -9948,18 +9958,18 @@
       <c r="D189" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E189" s="8" t="s">
+      <c r="E189" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G189" s="3"/>
-      <c r="H189" s="8" t="s">
+      <c r="H189" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
         <v>439</v>
       </c>
@@ -9972,18 +9982,18 @@
       <c r="D190" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E190" s="8" t="s">
+      <c r="E190" s="3" t="s">
         <v>279</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G190" s="3"/>
-      <c r="H190" s="8" t="s">
+      <c r="H190" s="3" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
         <v>439</v>
       </c>
@@ -9996,18 +10006,18 @@
       <c r="D191" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E191" s="8" t="s">
+      <c r="E191" s="3" t="s">
         <v>279</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G191" s="3"/>
-      <c r="H191" s="8" t="s">
+      <c r="H191" s="3" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
         <v>439</v>
       </c>
@@ -10020,18 +10030,18 @@
       <c r="D192" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E192" s="8" t="s">
+      <c r="E192" s="3" t="s">
         <v>280</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G192" s="3"/>
-      <c r="H192" s="8" t="s">
+      <c r="H192" s="3" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
         <v>439</v>
       </c>
@@ -10044,18 +10054,18 @@
       <c r="D193" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E193" s="8" t="s">
+      <c r="E193" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G193" s="3"/>
-      <c r="H193" s="8" t="s">
+      <c r="H193" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>439</v>
       </c>
@@ -10068,18 +10078,18 @@
       <c r="D194" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E194" s="8" t="s">
+      <c r="E194" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G194" s="3"/>
-      <c r="H194" s="8" t="s">
+      <c r="H194" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
         <v>439</v>
       </c>
@@ -10092,18 +10102,18 @@
       <c r="D195" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E195" s="8" t="s">
+      <c r="E195" s="3" t="s">
         <v>372</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G195" s="3"/>
-      <c r="H195" s="8" t="s">
+      <c r="H195" s="3" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
         <v>439</v>
       </c>
@@ -10116,18 +10126,18 @@
       <c r="D196" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E196" s="8" t="s">
+      <c r="E196" s="3" t="s">
         <v>183</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G196" s="3"/>
-      <c r="H196" s="8" t="s">
+      <c r="H196" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
         <v>439</v>
       </c>
@@ -10140,18 +10150,18 @@
       <c r="D197" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E197" s="8" t="s">
+      <c r="E197" s="3" t="s">
         <v>183</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G197" s="3"/>
-      <c r="H197" s="8" t="s">
+      <c r="H197" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
         <v>439</v>
       </c>
@@ -10164,18 +10174,18 @@
       <c r="D198" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E198" s="8" t="s">
+      <c r="E198" s="3" t="s">
         <v>183</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G198" s="3"/>
-      <c r="H198" s="8" t="s">
+      <c r="H198" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
         <v>439</v>
       </c>
@@ -10188,18 +10198,18 @@
       <c r="D199" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E199" s="8" t="s">
+      <c r="E199" s="3" t="s">
         <v>352</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G199" s="3"/>
-      <c r="H199" s="8" t="s">
+      <c r="H199" s="3" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
         <v>439</v>
       </c>
@@ -10212,18 +10222,18 @@
       <c r="D200" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E200" s="8" t="s">
+      <c r="E200" s="3" t="s">
         <v>352</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G200" s="3"/>
-      <c r="H200" s="8" t="s">
+      <c r="H200" s="3" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
         <v>439</v>
       </c>
@@ -10236,18 +10246,18 @@
       <c r="D201" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E201" s="8" t="s">
+      <c r="E201" s="3" t="s">
         <v>352</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G201" s="3"/>
-      <c r="H201" s="8" t="s">
+      <c r="H201" s="3" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
         <v>439</v>
       </c>
@@ -10260,18 +10270,18 @@
       <c r="D202" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E202" s="8" t="s">
+      <c r="E202" s="3" t="s">
         <v>352</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G202" s="3"/>
-      <c r="H202" s="8" t="s">
+      <c r="H202" s="3" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
         <v>439</v>
       </c>
@@ -10284,18 +10294,18 @@
       <c r="D203" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E203" s="8" t="s">
+      <c r="E203" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G203" s="3"/>
-      <c r="H203" s="8" t="s">
+      <c r="H203" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
         <v>439</v>
       </c>
@@ -10308,18 +10318,18 @@
       <c r="D204" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E204" s="8" t="s">
+      <c r="E204" s="3" t="s">
         <v>159</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G204" s="3"/>
-      <c r="H204" s="8" t="s">
+      <c r="H204" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
         <v>439</v>
       </c>
@@ -10332,18 +10342,18 @@
       <c r="D205" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E205" s="8" t="s">
+      <c r="E205" s="3" t="s">
         <v>183</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G205" s="3"/>
-      <c r="H205" s="8" t="s">
+      <c r="H205" s="3" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
         <v>439</v>
       </c>
@@ -10356,18 +10366,18 @@
       <c r="D206" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E206" s="8">
+      <c r="E206" s="3">
         <v>34</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G206" s="3"/>
-      <c r="H206" s="8">
+      <c r="H206" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
         <v>439</v>
       </c>
@@ -10380,18 +10390,18 @@
       <c r="D207" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E207" s="8">
+      <c r="E207" s="3">
         <v>34</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G207" s="3"/>
-      <c r="H207" s="8">
+      <c r="H207" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
         <v>439</v>
       </c>
@@ -10404,18 +10414,18 @@
       <c r="D208" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E208" s="8">
+      <c r="E208" s="3">
         <v>12</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G208" s="3"/>
-      <c r="H208" s="8">
+      <c r="H208" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
         <v>439</v>
       </c>
@@ -10428,18 +10438,18 @@
       <c r="D209" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E209" s="8">
+      <c r="E209" s="3">
         <v>12</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G209" s="3"/>
-      <c r="H209" s="8">
+      <c r="H209" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
         <v>439</v>
       </c>
@@ -10452,18 +10462,18 @@
       <c r="D210" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E210" s="8">
+      <c r="E210" s="3">
         <v>46</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G210" s="3"/>
-      <c r="H210" s="8">
+      <c r="H210" s="3">
         <v>46</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>439</v>
       </c>
@@ -10476,18 +10486,18 @@
       <c r="D211" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E211" s="8">
+      <c r="E211" s="3">
         <v>32</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G211" s="3"/>
-      <c r="H211" s="8">
+      <c r="H211" s="3">
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
         <v>439</v>
       </c>
@@ -10500,18 +10510,18 @@
       <c r="D212" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E212" s="8">
+      <c r="E212" s="3">
         <v>40</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G212" s="3"/>
-      <c r="H212" s="8">
+      <c r="H212" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
         <v>439</v>
       </c>
@@ -10524,18 +10534,18 @@
       <c r="D213" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E213" s="8">
+      <c r="E213" s="3">
         <v>30</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G213" s="3"/>
-      <c r="H213" s="8">
+      <c r="H213" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
         <v>439</v>
       </c>
@@ -10548,18 +10558,18 @@
       <c r="D214" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E214" s="8">
+      <c r="E214" s="3">
         <v>26</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G214" s="3"/>
-      <c r="H214" s="8">
+      <c r="H214" s="3">
         <v>26</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
         <v>439</v>
       </c>
@@ -10572,18 +10582,18 @@
       <c r="D215" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="E215" s="8" t="s">
+      <c r="E215" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G215" s="3"/>
-      <c r="H215" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H215" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
         <v>439</v>
       </c>
@@ -10596,18 +10606,18 @@
       <c r="D216" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="E216" s="8" t="s">
+      <c r="E216" s="3" t="s">
         <v>496</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G216" s="3"/>
-      <c r="H216" s="8" t="s">
+      <c r="H216" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
         <v>439</v>
       </c>
@@ -10620,18 +10630,18 @@
       <c r="D217" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="E217" s="8" t="s">
+      <c r="E217" s="3" t="s">
         <v>499</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G217" s="3"/>
-      <c r="H217" s="8" t="s">
+      <c r="H217" s="3" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
         <v>439</v>
       </c>
@@ -10644,18 +10654,18 @@
       <c r="D218" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="E218" s="8" t="s">
+      <c r="E218" s="3" t="s">
         <v>501</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G218" s="3"/>
-      <c r="H218" s="8" t="s">
+      <c r="H218" s="3" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
         <v>439</v>
       </c>
@@ -10668,16 +10678,16 @@
       <c r="D219" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E219" s="8" t="s">
+      <c r="E219" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G219" s="3"/>
-      <c r="H219" s="8"/>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H219" s="3"/>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
         <v>439</v>
       </c>
@@ -10690,16 +10700,16 @@
       <c r="D220" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="E220" s="8" t="s">
+      <c r="E220" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G220" s="3"/>
-      <c r="H220" s="8"/>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H220" s="3"/>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
         <v>439</v>
       </c>
@@ -10712,16 +10722,16 @@
       <c r="D221" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="E221" s="8" t="s">
+      <c r="E221" s="3" t="s">
         <v>372</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G221" s="3"/>
-      <c r="H221" s="8"/>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H221" s="3"/>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
         <v>439</v>
       </c>
@@ -10734,16 +10744,16 @@
       <c r="D222" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E222" s="8" t="s">
+      <c r="E222" s="3" t="s">
         <v>267</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G222" s="3"/>
-      <c r="H222" s="8"/>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H222" s="3"/>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
         <v>439</v>
       </c>
@@ -10756,18 +10766,18 @@
       <c r="D223" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E223" s="8" t="s">
+      <c r="E223" s="3" t="s">
         <v>408</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G223" s="3"/>
-      <c r="H223" s="8" t="s">
+      <c r="H223" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
         <v>439</v>
       </c>
@@ -10780,18 +10790,18 @@
       <c r="D224" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E224" s="8" t="s">
+      <c r="E224" s="3" t="s">
         <v>409</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G224" s="3"/>
-      <c r="H224" s="8" t="s">
+      <c r="H224" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
         <v>439</v>
       </c>
@@ -10804,18 +10814,18 @@
       <c r="D225" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="E225" s="8" t="s">
+      <c r="E225" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G225" s="3"/>
-      <c r="H225" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H225" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="3" t="s">
         <v>439</v>
       </c>
@@ -10828,18 +10838,18 @@
       <c r="D226" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E226" s="8" t="s">
+      <c r="E226" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G226" s="3"/>
-      <c r="H226" s="8" t="s">
+      <c r="H226" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="3" t="s">
         <v>439</v>
       </c>
@@ -10852,18 +10862,18 @@
       <c r="D227" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E227" s="8" t="s">
+      <c r="E227" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G227" s="3"/>
-      <c r="H227" s="8" t="s">
+      <c r="H227" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="3" t="s">
         <v>439</v>
       </c>
@@ -10876,18 +10886,18 @@
       <c r="D228" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E228" s="8" t="s">
+      <c r="E228" s="3" t="s">
         <v>200</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G228" s="3"/>
-      <c r="H228" s="8" t="s">
+      <c r="H228" s="3" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="3" t="s">
         <v>439</v>
       </c>
@@ -10900,18 +10910,18 @@
       <c r="D229" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E229" s="8" t="s">
+      <c r="E229" s="3" t="s">
         <v>410</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G229" s="3"/>
-      <c r="H229" s="8" t="s">
+      <c r="H229" s="3" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
         <v>439</v>
       </c>
@@ -10924,18 +10934,18 @@
       <c r="D230" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E230" s="8" t="s">
+      <c r="E230" s="3" t="s">
         <v>321</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G230" s="3"/>
-      <c r="H230" s="8" t="s">
+      <c r="H230" s="3" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
         <v>439</v>
       </c>
@@ -10948,16 +10958,16 @@
       <c r="D231" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E231" s="8"/>
+      <c r="E231" s="3"/>
       <c r="F231" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G231" s="3"/>
-      <c r="H231" s="8" t="s">
+      <c r="H231" s="3" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
         <v>439</v>
       </c>
@@ -10970,18 +10980,18 @@
       <c r="D232" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="E232" s="8" t="s">
+      <c r="E232" s="3" t="s">
         <v>324</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G232" s="3"/>
-      <c r="H232" s="8" t="s">
+      <c r="H232" s="3" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
         <v>439</v>
       </c>
@@ -10994,16 +11004,16 @@
       <c r="D233" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="E233" s="8"/>
+      <c r="E233" s="3"/>
       <c r="F233" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G233" s="3"/>
-      <c r="H233" s="8" t="s">
+      <c r="H233" s="3" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
         <v>439</v>
       </c>
@@ -11016,18 +11026,18 @@
       <c r="D234" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E234" s="8" t="s">
+      <c r="E234" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G234" s="3"/>
-      <c r="H234" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H234" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
         <v>439</v>
       </c>
@@ -11040,18 +11050,18 @@
       <c r="D235" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E235" s="8" t="s">
+      <c r="E235" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G235" s="3"/>
-      <c r="H235" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H235" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
         <v>439</v>
       </c>
@@ -11064,18 +11074,18 @@
       <c r="D236" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="E236" s="8" t="s">
+      <c r="E236" s="3" t="s">
         <v>411</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G236" s="3"/>
-      <c r="H236" s="8" t="s">
+      <c r="H236" s="3" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
         <v>439</v>
       </c>
@@ -11088,18 +11098,18 @@
       <c r="D237" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="E237" s="8" t="s">
+      <c r="E237" s="3" t="s">
         <v>411</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G237" s="3"/>
-      <c r="H237" s="8" t="s">
+      <c r="H237" s="3" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
         <v>439</v>
       </c>
@@ -11112,18 +11122,18 @@
       <c r="D238" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E238" s="8" t="s">
+      <c r="E238" s="3" t="s">
         <v>411</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G238" s="3"/>
-      <c r="H238" s="8" t="s">
+      <c r="H238" s="3" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
         <v>439</v>
       </c>
@@ -11136,18 +11146,18 @@
       <c r="D239" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="E239" s="8" t="s">
+      <c r="E239" s="3" t="s">
         <v>411</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G239" s="3"/>
-      <c r="H239" s="8" t="s">
+      <c r="H239" s="3" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
         <v>439</v>
       </c>
@@ -11160,18 +11170,18 @@
       <c r="D240" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E240" s="8" t="s">
+      <c r="E240" s="3" t="s">
         <v>411</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G240" s="3"/>
-      <c r="H240" s="8" t="s">
+      <c r="H240" s="3" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
         <v>439</v>
       </c>
@@ -11184,18 +11194,18 @@
       <c r="D241" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E241" s="8" t="s">
+      <c r="E241" s="3" t="s">
         <v>411</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G241" s="3"/>
-      <c r="H241" s="8" t="s">
+      <c r="H241" s="3" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
         <v>439</v>
       </c>
@@ -11208,18 +11218,18 @@
       <c r="D242" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="E242" s="8" t="s">
+      <c r="E242" s="3" t="s">
         <v>284</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G242" s="3"/>
-      <c r="H242" s="8" t="s">
+      <c r="H242" s="3" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
         <v>439</v>
       </c>
@@ -11232,18 +11242,18 @@
       <c r="D243" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E243" s="8" t="s">
+      <c r="E243" s="3" t="s">
         <v>326</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G243" s="3"/>
-      <c r="H243" s="8" t="s">
+      <c r="H243" s="3" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
         <v>439</v>
       </c>
@@ -11256,18 +11266,18 @@
       <c r="D244" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E244" s="8" t="s">
+      <c r="E244" s="3" t="s">
         <v>210</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G244" s="3"/>
-      <c r="H244" s="8" t="s">
+      <c r="H244" s="3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
         <v>439</v>
       </c>
@@ -11280,18 +11290,18 @@
       <c r="D245" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E245" s="8" t="s">
+      <c r="E245" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G245" s="3"/>
-      <c r="H245" s="8" t="s">
+      <c r="H245" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
         <v>439</v>
       </c>
@@ -11304,18 +11314,18 @@
       <c r="D246" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E246" s="8" t="s">
+      <c r="E246" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G246" s="3"/>
-      <c r="H246" s="8" t="s">
+      <c r="H246" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="3" t="s">
         <v>439</v>
       </c>
@@ -11328,18 +11338,18 @@
       <c r="D247" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E247" s="8" t="s">
+      <c r="E247" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G247" s="3"/>
-      <c r="H247" s="8" t="s">
+      <c r="H247" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="3" t="s">
         <v>439</v>
       </c>
@@ -11352,18 +11362,18 @@
       <c r="D248" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E248" s="8" t="s">
+      <c r="E248" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G248" s="3"/>
-      <c r="H248" s="8" t="s">
+      <c r="H248" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
         <v>439</v>
       </c>
@@ -11376,18 +11386,18 @@
       <c r="D249" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E249" s="8" t="s">
+      <c r="E249" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G249" s="3"/>
-      <c r="H249" s="8" t="s">
+      <c r="H249" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
         <v>439</v>
       </c>
@@ -11400,18 +11410,18 @@
       <c r="D250" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E250" s="8" t="s">
+      <c r="E250" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G250" s="3"/>
-      <c r="H250" s="8" t="s">
+      <c r="H250" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
         <v>439</v>
       </c>
@@ -11424,18 +11434,18 @@
       <c r="D251" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E251" s="8" t="s">
+      <c r="E251" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G251" s="3"/>
-      <c r="H251" s="8" t="s">
+      <c r="H251" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
         <v>439</v>
       </c>
@@ -11448,18 +11458,18 @@
       <c r="D252" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E252" s="8" t="s">
+      <c r="E252" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G252" s="3"/>
-      <c r="H252" s="8" t="s">
+      <c r="H252" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
         <v>439</v>
       </c>
@@ -11472,18 +11482,18 @@
       <c r="D253" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E253" s="8" t="s">
+      <c r="E253" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G253" s="3"/>
-      <c r="H253" s="8" t="s">
+      <c r="H253" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
         <v>439</v>
       </c>
@@ -11496,18 +11506,18 @@
       <c r="D254" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E254" s="8" t="s">
+      <c r="E254" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G254" s="3"/>
-      <c r="H254" s="8" t="s">
+      <c r="H254" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
         <v>439</v>
       </c>
@@ -11520,18 +11530,18 @@
       <c r="D255" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E255" s="8" t="s">
+      <c r="E255" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G255" s="3"/>
-      <c r="H255" s="8" t="s">
+      <c r="H255" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
         <v>439</v>
       </c>
@@ -11544,18 +11554,18 @@
       <c r="D256" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E256" s="8" t="s">
+      <c r="E256" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G256" s="3"/>
-      <c r="H256" s="8" t="s">
+      <c r="H256" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
         <v>439</v>
       </c>
@@ -11568,18 +11578,18 @@
       <c r="D257" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E257" s="8" t="s">
+      <c r="E257" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G257" s="3"/>
-      <c r="H257" s="8" t="s">
+      <c r="H257" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
         <v>439</v>
       </c>
@@ -11592,18 +11602,18 @@
       <c r="D258" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E258" s="8" t="s">
+      <c r="E258" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G258" s="3"/>
-      <c r="H258" s="8" t="s">
+      <c r="H258" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
         <v>439</v>
       </c>
@@ -11616,18 +11626,18 @@
       <c r="D259" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E259" s="8" t="s">
+      <c r="E259" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G259" s="3"/>
-      <c r="H259" s="8" t="s">
+      <c r="H259" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="3" t="s">
         <v>439</v>
       </c>
@@ -11640,18 +11650,18 @@
       <c r="D260" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E260" s="8" t="s">
+      <c r="E260" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G260" s="3"/>
-      <c r="H260" s="8" t="s">
+      <c r="H260" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="3" t="s">
         <v>439</v>
       </c>
@@ -11664,18 +11674,18 @@
       <c r="D261" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E261" s="8" t="s">
+      <c r="E261" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G261" s="3"/>
-      <c r="H261" s="8" t="s">
+      <c r="H261" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
         <v>439</v>
       </c>
@@ -11688,18 +11698,18 @@
       <c r="D262" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E262" s="8" t="s">
+      <c r="E262" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G262" s="3"/>
-      <c r="H262" s="8" t="s">
+      <c r="H262" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
         <v>439</v>
       </c>
@@ -11712,18 +11722,18 @@
       <c r="D263" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E263" s="8" t="s">
+      <c r="E263" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G263" s="3"/>
-      <c r="H263" s="8" t="s">
+      <c r="H263" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
         <v>439</v>
       </c>
@@ -11736,18 +11746,18 @@
       <c r="D264" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E264" s="8" t="s">
+      <c r="E264" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G264" s="3"/>
-      <c r="H264" s="8" t="s">
+      <c r="H264" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
         <v>439</v>
       </c>
@@ -11760,18 +11770,18 @@
       <c r="D265" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E265" s="8" t="s">
+      <c r="E265" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G265" s="3"/>
-      <c r="H265" s="8" t="s">
+      <c r="H265" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
         <v>439</v>
       </c>
@@ -11784,18 +11794,18 @@
       <c r="D266" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E266" s="8" t="s">
+      <c r="E266" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G266" s="3"/>
-      <c r="H266" s="8" t="s">
+      <c r="H266" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="3" t="s">
         <v>439</v>
       </c>
@@ -11808,62 +11818,62 @@
       <c r="D267" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E267" s="8" t="s">
+      <c r="E267" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G267" s="3"/>
-      <c r="H267" s="8" t="s">
+      <c r="H267" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A268" s="13" t="s">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A268" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="B268" s="13" t="s">
+      <c r="B268" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="C268" s="13" t="s">
+      <c r="C268" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="D268" s="13" t="s">
+      <c r="D268" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="E268" s="14" t="s">
+      <c r="E268" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="F268" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G268" s="13"/>
-      <c r="H268" s="14" t="s">
+      <c r="F268" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G268" s="10"/>
+      <c r="H268" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A269" s="13" t="s">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A269" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="B269" s="13" t="s">
+      <c r="B269" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="C269" s="13" t="s">
+      <c r="C269" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="D269" s="13" t="s">
+      <c r="D269" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="E269" s="14" t="s">
+      <c r="E269" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="F269" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G269" s="13"/>
-      <c r="H269" s="14" t="s">
+      <c r="F269" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G269" s="10"/>
+      <c r="H269" s="10" t="s">
         <v>17</v>
       </c>
     </row>

--- a/app/nsa_sa/DB.xlsx
+++ b/app/nsa_sa/DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aj_mac/Documents/Atel/server/code/app/nsa_sa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D9FEAC-9BF6-9E4F-8507-4E21746A98D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6B1280-0E7C-DD44-AF76-64D442A98EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15960" activeTab="5" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
+    <workbookView xWindow="-20" yWindow="620" windowWidth="14400" windowHeight="16120" firstSheet="1" activeTab="5" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
   </bookViews>
   <sheets>
     <sheet name="TermPointToAmf" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="MOC" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MOC!$A$1:$F$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MOC!$A$1:$F$293</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="505">
   <si>
     <t>5qi1</t>
   </si>
@@ -1497,6 +1497,66 @@
   </si>
   <si>
     <t>[{"sd":  "1", "sst":  "1"}]</t>
+  </si>
+  <si>
+    <t>UPW</t>
+  </si>
+  <si>
+    <t>2401:4900:8:605::4</t>
+  </si>
+  <si>
+    <t>::</t>
+  </si>
+  <si>
+    <t>2401:4900:8:60c::4</t>
+  </si>
+  <si>
+    <t>GNBCUCPFunction=1,EUtraNetwork=1,EUtranFrequency=2545</t>
+  </si>
+  <si>
+    <t>GNBCUCPFunction=1,UeMC=1,UeMCEUtranFreqRelProfile=L850</t>
+  </si>
+  <si>
+    <t>GNBCUCPFunction=1,EUtraNetwork=1,EUtranFrequency=1526</t>
+  </si>
+  <si>
+    <t>GNBCUCPFunction=1,EUtraNetwork=1,EUtranFrequency=365</t>
+  </si>
+  <si>
+    <t>GNBCUCPFunction=1,EUtraNetwork=1,EUtranFrequency=39348</t>
+  </si>
+  <si>
+    <t>GNBCUCPFunction=1,EUtraNetwork=1,EUtranFrequency=39349</t>
+  </si>
+  <si>
+    <t>SystemFunctions=1,Lm=1,FeatureState=CXC4012503</t>
+  </si>
+  <si>
+    <t>SystemFunctions=1,Lm=1,FeatureState=CXC4012589</t>
+  </si>
+  <si>
+    <t>SystemFunctions=1,Lm=1,FeatureState=CXC4012668</t>
+  </si>
+  <si>
+    <t>SystemFunctions=1,Lm=1,FeatureState=CXC4012673</t>
+  </si>
+  <si>
+    <t>SystemFunctions=1,Lm=1,FeatureState=CXC4012635</t>
+  </si>
+  <si>
+    <t>pZeroNomPuschGrant</t>
+  </si>
+  <si>
+    <t>-102</t>
+  </si>
+  <si>
+    <t>pZeroNomSrs</t>
+  </si>
+  <si>
+    <t>GNBCUCPFunction=1,CUCP5qiTable=1,CUCP5qi=5qi5</t>
+  </si>
+  <si>
+    <t>GNBCUCPFunction=1,CUCP5qiTable=1,CUCP5qi=5qi6</t>
   </si>
 </sst>
 </file>
@@ -1932,7 +1992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247B63BC-5D3A-4B06-850D-E1325BAD072A}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -2202,6 +2262,64 @@
         <v>17</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>432</v>
       </c>
     </row>
@@ -3665,158 +3783,438 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
+      <c r="A24" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B24" s="6">
+        <v>2545</v>
+      </c>
+      <c r="C24" s="6">
+        <v>25</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="6">
+        <v>5</v>
+      </c>
+      <c r="F24" s="6">
+        <v>5</v>
+      </c>
+      <c r="G24" s="6">
+        <v>23</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="6">
+        <v>-128</v>
+      </c>
+      <c r="J24" s="6">
+        <v>2</v>
+      </c>
+      <c r="K24" s="6">
+        <v>62</v>
+      </c>
+      <c r="L24" s="6">
+        <v>16</v>
+      </c>
+      <c r="M24" s="6">
+        <v>2</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q24" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T24" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
+      <c r="A25" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B25" s="6">
+        <v>1526</v>
+      </c>
+      <c r="C25" s="6">
+        <v>75</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="6">
+        <v>3</v>
+      </c>
+      <c r="F25" s="6">
+        <v>3</v>
+      </c>
+      <c r="G25" s="6">
+        <v>23</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="6">
+        <v>-128</v>
+      </c>
+      <c r="J25" s="6">
+        <v>2</v>
+      </c>
+      <c r="K25" s="6">
+        <v>62</v>
+      </c>
+      <c r="L25" s="6">
+        <v>16</v>
+      </c>
+      <c r="M25" s="6">
+        <v>2</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T25" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
+      <c r="A26" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B26" s="6">
+        <v>365</v>
+      </c>
+      <c r="C26" s="6">
+        <v>75</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="6">
+        <v>6</v>
+      </c>
+      <c r="F26" s="6">
+        <v>6</v>
+      </c>
+      <c r="G26" s="6">
+        <v>23</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="6">
+        <v>-128</v>
+      </c>
+      <c r="J26" s="6">
+        <v>2</v>
+      </c>
+      <c r="K26" s="6">
+        <v>62</v>
+      </c>
+      <c r="L26" s="6">
+        <v>16</v>
+      </c>
+      <c r="M26" s="6">
+        <v>6</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T26" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
+      <c r="A27" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B27" s="6">
+        <v>39150</v>
+      </c>
+      <c r="C27" s="6">
+        <v>100</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="6">
+        <v>4</v>
+      </c>
+      <c r="F27" s="6">
+        <v>4</v>
+      </c>
+      <c r="G27" s="6">
+        <v>23</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="6">
+        <v>-128</v>
+      </c>
+      <c r="J27" s="6">
+        <v>2</v>
+      </c>
+      <c r="K27" s="6">
+        <v>62</v>
+      </c>
+      <c r="L27" s="6">
+        <v>16</v>
+      </c>
+      <c r="M27" s="6">
+        <v>1</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T27" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
+      <c r="A28" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B28" s="6">
+        <v>39348</v>
+      </c>
+      <c r="C28" s="6">
+        <v>100</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="6">
+        <v>4</v>
+      </c>
+      <c r="F28" s="6">
+        <v>4</v>
+      </c>
+      <c r="G28" s="6">
+        <v>23</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="6">
+        <v>-128</v>
+      </c>
+      <c r="J28" s="6">
+        <v>2</v>
+      </c>
+      <c r="K28" s="6">
+        <v>62</v>
+      </c>
+      <c r="L28" s="6">
+        <v>16</v>
+      </c>
+      <c r="M28" s="6">
+        <v>1</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="R28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T28" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
+      <c r="A29" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B29" s="6">
+        <v>39151</v>
+      </c>
+      <c r="C29" s="6">
+        <v>100</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="6">
+        <v>4</v>
+      </c>
+      <c r="F29" s="6">
+        <v>4</v>
+      </c>
+      <c r="G29" s="6">
+        <v>23</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="6">
+        <v>-128</v>
+      </c>
+      <c r="J29" s="6">
+        <v>2</v>
+      </c>
+      <c r="K29" s="6">
+        <v>62</v>
+      </c>
+      <c r="L29" s="6">
+        <v>16</v>
+      </c>
+      <c r="M29" s="6">
+        <v>1</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q29" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="R29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T29" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
+      <c r="A30" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B30" s="6">
+        <v>39349</v>
+      </c>
+      <c r="C30" s="6">
+        <v>100</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="6">
+        <v>4</v>
+      </c>
+      <c r="F30" s="6">
+        <v>4</v>
+      </c>
+      <c r="G30" s="6">
+        <v>23</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="6">
+        <v>-128</v>
+      </c>
+      <c r="J30" s="6">
+        <v>2</v>
+      </c>
+      <c r="K30" s="6">
+        <v>62</v>
+      </c>
+      <c r="L30" s="6">
+        <v>16</v>
+      </c>
+      <c r="M30" s="6">
+        <v>1</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="T30" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
@@ -4532,8 +4930,8 @@
       <c r="N10" s="4">
         <v>25</v>
       </c>
-      <c r="O10" s="4">
-        <v>25</v>
+      <c r="O10" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -4710,7 +5108,7 @@
         <v>200</v>
       </c>
       <c r="H6" s="4">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -4736,7 +5134,7 @@
         <v>200</v>
       </c>
       <c r="H7" s="4">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -5322,14 +5720,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04129BFA-1C57-4A9F-9E8B-6ECAA0BFBBBF}">
-  <dimension ref="A1:G269"/>
+  <dimension ref="A1:G295"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.1640625" style="8" customWidth="1"/>
     <col min="3" max="3" width="46.83203125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="24.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.83203125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="8" customWidth="1"/>
     <col min="6" max="6" width="6" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="8.6640625" style="7"/>
@@ -5360,88 +5758,88 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>164</v>
+        <v>458</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>482</v>
+        <v>393</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>18</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>167</v>
+        <v>459</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>483</v>
+        <v>393</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>18</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>186</v>
+        <v>460</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>225</v>
+        <v>355</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>484</v>
+        <v>393</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>221</v>
+        <v>461</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>222</v>
+        <v>355</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>17</v>
+        <v>393</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>18</v>
@@ -5452,19 +5850,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>221</v>
+        <v>462</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>223</v>
+        <v>355</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>17</v>
+        <v>393</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>18</v>
@@ -5475,22 +5873,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>221</v>
+        <v>418</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>224</v>
+        <v>355</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>17</v>
+        <v>393</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>424</v>
@@ -5504,18 +5902,20 @@
         <v>420</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>355</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="9"/>
+      <c r="G8" s="9" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
@@ -5525,10 +5925,10 @@
         <v>420</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>459</v>
+        <v>135</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>355</v>
+        <v>136</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>393</v>
@@ -5536,7 +5936,9 @@
       <c r="F9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="9"/>
+      <c r="G9" s="9" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
@@ -5546,97 +5948,105 @@
         <v>420</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>460</v>
+        <v>135</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>355</v>
+        <v>137</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>393</v>
+        <v>138</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="9"/>
+      <c r="G10" s="9" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>461</v>
+        <v>164</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>393</v>
+        <v>482</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="9"/>
+      <c r="G11" s="9" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>462</v>
+        <v>167</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="9"/>
+      <c r="G12" s="9" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>463</v>
+        <v>186</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>355</v>
+        <v>225</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="9"/>
+      <c r="G13" s="9" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>393</v>
+        <v>17</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>18</v>
@@ -5647,19 +6057,19 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>18</v>
@@ -5669,25 +6079,27 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="3"/>
+      <c r="A16" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
@@ -5700,10 +6112,10 @@
         <v>164</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>17</v>
+        <v>168</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>17</v>
@@ -5718,13 +6130,13 @@
         <v>420</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>17</v>
@@ -5742,10 +6154,10 @@
         <v>167</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>17</v>
+        <v>168</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>17</v>
@@ -5760,10 +6172,10 @@
         <v>420</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>313</v>
+        <v>167</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>314</v>
+        <v>166</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>17</v>
@@ -5781,13 +6193,13 @@
         <v>420</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>379</v>
+        <v>17</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>17</v>
@@ -5805,10 +6217,10 @@
         <v>315</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>16</v>
+        <v>379</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>17</v>
@@ -5826,10 +6238,10 @@
         <v>315</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>17</v>
@@ -5847,10 +6259,10 @@
         <v>315</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>193</v>
+        <v>56</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>17</v>
@@ -5868,10 +6280,10 @@
         <v>315</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>56</v>
+        <v>193</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>17</v>
@@ -5886,13 +6298,13 @@
         <v>420</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="3">
-        <v>34</v>
+        <v>320</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>17</v>
@@ -5907,7 +6319,7 @@
         <v>420</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>93</v>
@@ -5928,13 +6340,13 @@
         <v>420</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E28" s="3">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>17</v>
@@ -5949,7 +6361,7 @@
         <v>420</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>93</v>
@@ -5970,13 +6382,13 @@
         <v>420</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E30" s="3">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>17</v>
@@ -5991,13 +6403,13 @@
         <v>420</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E31" s="3">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>17</v>
@@ -6012,13 +6424,13 @@
         <v>420</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E32" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>17</v>
@@ -6033,13 +6445,13 @@
         <v>420</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E33" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>17</v>
@@ -6054,13 +6466,13 @@
         <v>420</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E34" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>17</v>
@@ -6075,13 +6487,13 @@
         <v>420</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>139</v>
+        <v>346</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>158</v>
+        <v>93</v>
+      </c>
+      <c r="E35" s="3">
+        <v>26</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>17</v>
@@ -6099,7 +6511,7 @@
         <v>139</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>158</v>
@@ -6120,10 +6532,10 @@
         <v>139</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>17</v>
@@ -6141,10 +6553,10 @@
         <v>139</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>17</v>
@@ -6162,10 +6574,10 @@
         <v>139</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>17</v>
@@ -6183,10 +6595,10 @@
         <v>139</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>380</v>
+        <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>17</v>
@@ -6201,13 +6613,13 @@
         <v>420</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>162</v>
+        <v>380</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>17</v>
@@ -6225,10 +6637,10 @@
         <v>159</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>17</v>
@@ -6243,13 +6655,13 @@
         <v>420</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>17</v>
@@ -6267,10 +6679,10 @@
         <v>146</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>17</v>
@@ -6285,13 +6697,13 @@
         <v>420</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>17</v>
@@ -6309,10 +6721,10 @@
         <v>153</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>381</v>
+        <v>17</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>17</v>
@@ -6330,10 +6742,10 @@
         <v>153</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>17</v>
+        <v>381</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>17</v>
@@ -6351,7 +6763,7 @@
         <v>153</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>17</v>
@@ -6369,10 +6781,10 @@
         <v>420</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>17</v>
@@ -6390,10 +6802,10 @@
         <v>420</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>17</v>
@@ -6411,13 +6823,13 @@
         <v>420</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>232</v>
+        <v>151</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>17</v>
@@ -6435,10 +6847,10 @@
         <v>232</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>297</v>
+        <v>85</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>17</v>
@@ -6453,13 +6865,13 @@
         <v>420</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>234</v>
+        <v>297</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>17</v>
@@ -6474,13 +6886,13 @@
         <v>420</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>477</v>
+        <v>233</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>234</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>478</v>
+        <v>123</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>17</v>
@@ -6498,10 +6910,10 @@
         <v>477</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>479</v>
+        <v>234</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>123</v>
+        <v>478</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>17</v>
@@ -6519,7 +6931,7 @@
         <v>477</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>123</v>
@@ -6540,10 +6952,10 @@
         <v>477</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>269</v>
+        <v>480</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>17</v>
@@ -6558,13 +6970,13 @@
         <v>420</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>248</v>
+        <v>477</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>17</v>
+        <v>255</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>17</v>
@@ -6600,13 +7012,13 @@
         <v>420</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>382</v>
+        <v>17</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>17</v>
@@ -6624,10 +7036,10 @@
         <v>235</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>238</v>
+        <v>382</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>17</v>
@@ -6645,10 +7057,10 @@
         <v>235</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>383</v>
+        <v>238</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>17</v>
@@ -6666,7 +7078,7 @@
         <v>235</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>383</v>
@@ -6687,10 +7099,10 @@
         <v>235</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>18</v>
+        <v>383</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>17</v>
@@ -6708,10 +7120,10 @@
         <v>235</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>384</v>
+        <v>18</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>17</v>
@@ -6729,10 +7141,10 @@
         <v>235</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>244</v>
+        <v>384</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>17</v>
@@ -6750,10 +7162,10 @@
         <v>235</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>17</v>
@@ -6768,13 +7180,13 @@
         <v>420</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>17</v>
+        <v>246</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>17</v>
@@ -6792,10 +7204,10 @@
         <v>119</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>17</v>
@@ -6813,10 +7225,10 @@
         <v>119</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>17</v>
@@ -6831,13 +7243,13 @@
         <v>420</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>17</v>
@@ -6852,13 +7264,13 @@
         <v>420</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>17</v>
@@ -6876,10 +7288,10 @@
         <v>126</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>395</v>
+        <v>16</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>17</v>
@@ -6894,13 +7306,13 @@
         <v>420</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>253</v>
+        <v>126</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>254</v>
+        <v>128</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>255</v>
+        <v>395</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>17</v>
@@ -6915,10 +7327,10 @@
         <v>420</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>255</v>
@@ -6939,7 +7351,7 @@
         <v>275</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>255</v>
@@ -6957,12 +7369,14 @@
         <v>420</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E77" s="3"/>
+        <v>277</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>255</v>
+      </c>
       <c r="F77" s="3" t="s">
         <v>17</v>
       </c>
@@ -6976,14 +7390,12 @@
         <v>420</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>295</v>
+        <v>252</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>384</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
         <v>17</v>
       </c>
@@ -7000,10 +7412,10 @@
         <v>295</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>17</v>
+        <v>384</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>17</v>
@@ -7021,10 +7433,10 @@
         <v>295</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>17</v>
@@ -7042,10 +7454,10 @@
         <v>295</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>17</v>
@@ -7063,10 +7475,10 @@
         <v>295</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>421</v>
+        <v>285</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>17</v>
@@ -7084,10 +7496,10 @@
         <v>295</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>290</v>
+        <v>421</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>17</v>
@@ -7105,10 +7517,10 @@
         <v>295</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>17</v>
@@ -7123,13 +7535,13 @@
         <v>420</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>384</v>
+        <v>291</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>17</v>
@@ -7147,10 +7559,10 @@
         <v>296</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>18</v>
+        <v>384</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>17</v>
@@ -7168,10 +7580,10 @@
         <v>296</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>17</v>
@@ -7189,10 +7601,10 @@
         <v>296</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>283</v>
+        <v>73</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>17</v>
@@ -7210,10 +7622,10 @@
         <v>296</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>17</v>
@@ -7231,10 +7643,10 @@
         <v>296</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>17</v>
@@ -7252,10 +7664,10 @@
         <v>296</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>17</v>
@@ -7273,10 +7685,10 @@
         <v>296</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>17</v>
@@ -7294,10 +7706,10 @@
         <v>296</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>17</v>
@@ -7312,13 +7724,13 @@
         <v>420</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>16</v>
+        <v>294</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>17</v>
@@ -7336,10 +7748,10 @@
         <v>321</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>17</v>
@@ -7357,10 +7769,10 @@
         <v>321</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>17</v>
@@ -7378,10 +7790,10 @@
         <v>321</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>325</v>
+        <v>18</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>17</v>
@@ -7399,7 +7811,7 @@
         <v>321</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>325</v>
@@ -7417,13 +7829,13 @@
         <v>420</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>16</v>
+        <v>325</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>17</v>
@@ -7441,10 +7853,10 @@
         <v>326</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>17</v>
@@ -7462,10 +7874,10 @@
         <v>326</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>17</v>
@@ -7483,10 +7895,10 @@
         <v>326</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>327</v>
+        <v>17</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>17</v>
@@ -7504,7 +7916,7 @@
         <v>326</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>327</v>
@@ -7522,13 +7934,13 @@
         <v>420</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>16</v>
+        <v>327</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>17</v>
@@ -7546,10 +7958,10 @@
         <v>328</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>17</v>
@@ -7567,10 +7979,10 @@
         <v>328</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>17</v>
@@ -7588,10 +8000,10 @@
         <v>328</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>329</v>
+        <v>17</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>17</v>
@@ -7609,7 +8021,7 @@
         <v>328</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>329</v>
@@ -7627,13 +8039,13 @@
         <v>420</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>454</v>
+        <v>328</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>455</v>
+        <v>269</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>456</v>
+        <v>329</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>17</v>
@@ -7648,7 +8060,7 @@
         <v>420</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>455</v>
@@ -7669,13 +8081,13 @@
         <v>420</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>348</v>
+        <v>455</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>18</v>
+        <v>456</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>17</v>
@@ -7693,10 +8105,10 @@
         <v>419</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>17</v>
@@ -7711,13 +8123,13 @@
         <v>420</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>347</v>
+        <v>419</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>17</v>
@@ -7735,10 +8147,10 @@
         <v>347</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>17</v>
@@ -7753,13 +8165,13 @@
         <v>420</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>17</v>
+        <v>350</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>17</v>
@@ -7777,10 +8189,10 @@
         <v>351</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>350</v>
+        <v>17</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>17</v>
@@ -7795,13 +8207,13 @@
         <v>420</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>17</v>
+        <v>350</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>17</v>
@@ -7816,13 +8228,13 @@
         <v>420</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>221</v>
+        <v>503</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>57</v>
+        <v>107</v>
+      </c>
+      <c r="E118" s="3">
+        <v>20</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>17</v>
@@ -7837,12 +8249,14 @@
         <v>420</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>221</v>
+        <v>504</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E119" s="3"/>
+        <v>107</v>
+      </c>
+      <c r="E119" s="3">
+        <v>200</v>
+      </c>
       <c r="F119" s="3" t="s">
         <v>17</v>
       </c>
@@ -7859,10 +8273,10 @@
         <v>221</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>17</v>
@@ -7880,10 +8294,10 @@
         <v>221</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>17</v>
@@ -7901,11 +8315,9 @@
         <v>221</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>250</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="E122" s="3"/>
       <c r="F122" s="3" t="s">
         <v>17</v>
       </c>
@@ -7922,10 +8334,10 @@
         <v>221</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>251</v>
+        <v>39</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>17</v>
@@ -7943,10 +8355,10 @@
         <v>221</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>252</v>
+        <v>39</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>17</v>
@@ -7961,13 +8373,13 @@
         <v>420</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>170</v>
+        <v>249</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>178</v>
+        <v>250</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>17</v>
@@ -7982,13 +8394,13 @@
         <v>420</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>171</v>
+        <v>226</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>394</v>
+        <v>251</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>17</v>
@@ -8003,13 +8415,13 @@
         <v>420</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>16</v>
+        <v>252</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>17</v>
@@ -8027,10 +8439,10 @@
         <v>169</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>38</v>
+        <v>178</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>17</v>
@@ -8045,13 +8457,13 @@
         <v>420</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>168</v>
+        <v>394</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>17</v>
@@ -8066,13 +8478,13 @@
         <v>420</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>17</v>
@@ -8087,13 +8499,13 @@
         <v>420</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>17</v>
@@ -8111,10 +8523,10 @@
         <v>174</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>274</v>
+        <v>175</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>17</v>
@@ -8129,13 +8541,13 @@
         <v>420</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E133" s="3">
-        <v>1500</v>
+        <v>177</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>17</v>
@@ -8150,13 +8562,13 @@
         <v>420</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E134" s="3">
-        <v>600</v>
+        <v>176</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>17</v>
@@ -8171,13 +8583,13 @@
         <v>420</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E135" s="3">
-        <v>2000</v>
+        <v>274</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>17</v>
@@ -8195,10 +8607,10 @@
         <v>129</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E136" s="3">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>17</v>
@@ -8216,10 +8628,10 @@
         <v>129</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E137" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>17</v>
@@ -8234,13 +8646,13 @@
         <v>420</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>17</v>
+        <v>132</v>
+      </c>
+      <c r="E138" s="3">
+        <v>2000</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>17</v>
@@ -8255,13 +8667,13 @@
         <v>420</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>385</v>
+        <v>133</v>
+      </c>
+      <c r="E139" s="3">
+        <v>3000</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>17</v>
@@ -8276,13 +8688,13 @@
         <v>420</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>356</v>
+        <v>129</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>255</v>
+        <v>134</v>
+      </c>
+      <c r="E140" s="3">
+        <v>400</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>17</v>
@@ -8297,13 +8709,13 @@
         <v>420</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>356</v>
+        <v>180</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>269</v>
+        <v>181</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>363</v>
+        <v>17</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>17</v>
@@ -8318,13 +8730,13 @@
         <v>420</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>356</v>
+        <v>184</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>357</v>
+        <v>185</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>17</v>
@@ -8342,10 +8754,10 @@
         <v>356</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>358</v>
+        <v>268</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>361</v>
+        <v>255</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>17</v>
@@ -8363,10 +8775,10 @@
         <v>356</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>359</v>
+        <v>269</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>17</v>
@@ -8381,13 +8793,13 @@
         <v>420</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>199</v>
+        <v>356</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>195</v>
+        <v>357</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>17</v>
@@ -8402,13 +8814,13 @@
         <v>420</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>199</v>
+        <v>356</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>197</v>
+        <v>358</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>217</v>
+        <v>361</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>17</v>
@@ -8423,13 +8835,13 @@
         <v>420</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>199</v>
+        <v>356</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>196</v>
+        <v>359</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>17</v>
+        <v>360</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>17</v>
@@ -8444,13 +8856,13 @@
         <v>420</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>195</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>17</v>
@@ -8465,7 +8877,7 @@
         <v>420</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>197</v>
@@ -8486,7 +8898,7 @@
         <v>420</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>196</v>
@@ -8507,13 +8919,13 @@
         <v>420</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>195</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>17</v>
@@ -8528,13 +8940,13 @@
         <v>420</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>17</v>
@@ -8549,13 +8961,13 @@
         <v>420</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>17</v>
@@ -8570,13 +8982,13 @@
         <v>420</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>195</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>17</v>
@@ -8591,7 +9003,7 @@
         <v>420</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>196</v>
@@ -8612,7 +9024,7 @@
         <v>420</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>197</v>
@@ -8633,13 +9045,13 @@
         <v>420</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>195</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>17</v>
@@ -8654,7 +9066,7 @@
         <v>420</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>196</v>
@@ -8675,7 +9087,7 @@
         <v>420</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>197</v>
@@ -8696,13 +9108,13 @@
         <v>420</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>195</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>17</v>
@@ -8717,7 +9129,7 @@
         <v>420</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>196</v>
@@ -8738,7 +9150,7 @@
         <v>420</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>197</v>
@@ -8759,13 +9171,13 @@
         <v>420</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>218</v>
+        <v>386</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>17</v>
@@ -8780,13 +9192,13 @@
         <v>420</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>194</v>
+        <v>18</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>17</v>
@@ -8801,13 +9213,13 @@
         <v>420</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>17</v>
@@ -8822,13 +9234,13 @@
         <v>420</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>17</v>
@@ -8843,13 +9255,13 @@
         <v>420</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>17</v>
@@ -8864,13 +9276,13 @@
         <v>420</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>17</v>
@@ -8888,10 +9300,10 @@
         <v>212</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>17</v>
@@ -8906,13 +9318,13 @@
         <v>420</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>17</v>
@@ -8927,13 +9339,13 @@
         <v>420</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>17</v>
@@ -8948,13 +9360,13 @@
         <v>420</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>17</v>
@@ -8969,13 +9381,13 @@
         <v>420</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>17</v>
@@ -8990,13 +9402,13 @@
         <v>420</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>17</v>
@@ -9011,13 +9423,13 @@
         <v>420</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>364</v>
+        <v>210</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>17</v>
@@ -9032,13 +9444,13 @@
         <v>420</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>364</v>
+        <v>210</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>123</v>
+        <v>202</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>17</v>
@@ -9053,13 +9465,13 @@
         <v>420</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>364</v>
+        <v>210</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>17</v>
@@ -9077,10 +9489,10 @@
         <v>364</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>17</v>
@@ -9095,13 +9507,13 @@
         <v>420</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>17</v>
@@ -9116,13 +9528,13 @@
         <v>420</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>17</v>
@@ -9137,13 +9549,13 @@
         <v>420</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>17</v>
@@ -9158,13 +9570,13 @@
         <v>420</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>17</v>
@@ -9179,13 +9591,13 @@
         <v>420</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>17</v>
@@ -9200,13 +9612,13 @@
         <v>420</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>256</v>
+        <v>366</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>257</v>
+        <v>208</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>17</v>
@@ -9221,13 +9633,13 @@
         <v>420</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>258</v>
+        <v>366</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>259</v>
+        <v>209</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>17</v>
@@ -9242,13 +9654,13 @@
         <v>420</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>258</v>
+        <v>366</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>255</v>
+        <v>364</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>17</v>
@@ -9263,13 +9675,13 @@
         <v>420</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>17</v>
@@ -9281,16 +9693,16 @@
         <v>420</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>113</v>
+        <v>259</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>262</v>
+        <v>388</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>17</v>
@@ -9305,13 +9717,13 @@
         <v>420</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>182</v>
+        <v>258</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>123</v>
+        <v>255</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>17</v>
@@ -9326,13 +9738,13 @@
         <v>420</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>266</v>
+        <v>123</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>17</v>
@@ -9350,7 +9762,7 @@
         <v>265</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>266</v>
@@ -9371,10 +9783,10 @@
         <v>265</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>17</v>
@@ -9392,10 +9804,10 @@
         <v>265</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>268</v>
+        <v>112</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>17</v>
@@ -9413,7 +9825,7 @@
         <v>265</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>255</v>
@@ -9431,13 +9843,13 @@
         <v>420</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>353</v>
+        <v>265</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>269</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>354</v>
+        <v>255</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>17</v>
@@ -9452,13 +9864,13 @@
         <v>420</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>95</v>
+        <v>269</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>179</v>
+        <v>354</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>17</v>
@@ -9473,13 +9885,13 @@
         <v>420</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>330</v>
+        <v>263</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>95</v>
+        <v>264</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>179</v>
+        <v>18</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>17</v>
@@ -9491,16 +9903,16 @@
         <v>420</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>261</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>17</v>
@@ -9515,13 +9927,13 @@
         <v>420</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>331</v>
+        <v>263</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>95</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>335</v>
+        <v>179</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>17</v>
@@ -9536,13 +9948,13 @@
         <v>420</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>95</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>335</v>
+        <v>179</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>17</v>
@@ -9557,13 +9969,13 @@
         <v>420</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>333</v>
+        <v>261</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>95</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>335</v>
+        <v>179</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>17</v>
@@ -9578,7 +9990,7 @@
         <v>420</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>95</v>
@@ -9599,13 +10011,13 @@
         <v>420</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>53</v>
+        <v>335</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>17</v>
@@ -9620,13 +10032,13 @@
         <v>420</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>158</v>
+        <v>335</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>17</v>
@@ -9644,10 +10056,10 @@
         <v>334</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>179</v>
+        <v>335</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>17</v>
@@ -9662,13 +10074,13 @@
         <v>420</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>263</v>
+        <v>330</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E206" s="3">
-        <v>34</v>
+        <v>96</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>17</v>
@@ -9686,10 +10098,10 @@
         <v>330</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E207" s="3">
-        <v>34</v>
+        <v>110</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>17</v>
@@ -9704,13 +10116,13 @@
         <v>420</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E208" s="3">
-        <v>12</v>
+        <v>110</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>17</v>
@@ -9725,13 +10137,13 @@
         <v>420</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>337</v>
+        <v>263</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E209" s="3">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>17</v>
@@ -9746,13 +10158,13 @@
         <v>420</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>261</v>
+        <v>330</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E210" s="3">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>17</v>
@@ -9767,13 +10179,13 @@
         <v>420</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E211" s="3">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>17</v>
@@ -9788,13 +10200,13 @@
         <v>420</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E212" s="3">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>17</v>
@@ -9809,13 +10221,13 @@
         <v>420</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>333</v>
+        <v>261</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E213" s="3">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>17</v>
@@ -9830,13 +10242,13 @@
         <v>420</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E214" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>17</v>
@@ -9851,13 +10263,13 @@
         <v>420</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>466</v>
+        <v>332</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="E215" s="3" t="s">
-        <v>17</v>
+        <v>93</v>
+      </c>
+      <c r="E215" s="3">
+        <v>40</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>17</v>
@@ -9872,13 +10284,13 @@
         <v>420</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>466</v>
+        <v>333</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>474</v>
+        <v>93</v>
+      </c>
+      <c r="E216" s="3">
+        <v>30</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>17</v>
@@ -9893,13 +10305,13 @@
         <v>420</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>466</v>
+        <v>334</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="E217" s="3" t="s">
-        <v>475</v>
+        <v>93</v>
+      </c>
+      <c r="E217" s="3">
+        <v>26</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>17</v>
@@ -9914,13 +10326,13 @@
         <v>420</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>466</v>
+        <v>330</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>476</v>
+        <v>114</v>
+      </c>
+      <c r="E218" s="3">
+        <v>35</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>17</v>
@@ -9935,13 +10347,13 @@
         <v>420</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>466</v>
+        <v>330</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="E219" s="3" t="s">
-        <v>57</v>
+        <v>115</v>
+      </c>
+      <c r="E219" s="3">
+        <v>35</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>17</v>
@@ -9956,13 +10368,13 @@
         <v>420</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>466</v>
+        <v>261</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>57</v>
+        <v>112</v>
+      </c>
+      <c r="E220" s="3">
+        <v>12</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>17</v>
@@ -9977,13 +10389,13 @@
         <v>420</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>466</v>
+        <v>261</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>354</v>
+        <v>114</v>
+      </c>
+      <c r="E221" s="3">
+        <v>25</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>17</v>
@@ -9998,13 +10410,13 @@
         <v>420</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>466</v>
+        <v>261</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>255</v>
+        <v>115</v>
+      </c>
+      <c r="E222" s="3">
+        <v>25</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>17</v>
@@ -10019,13 +10431,13 @@
         <v>420</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>186</v>
+        <v>331</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E223" s="3" t="s">
-        <v>389</v>
+        <v>112</v>
+      </c>
+      <c r="E223" s="3">
+        <v>18</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>17</v>
@@ -10040,13 +10452,13 @@
         <v>420</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>186</v>
+        <v>331</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>390</v>
+        <v>114</v>
+      </c>
+      <c r="E224" s="3">
+        <v>25</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>17</v>
@@ -10061,13 +10473,13 @@
         <v>420</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>186</v>
+        <v>331</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E225" s="3" t="s">
-        <v>17</v>
+        <v>115</v>
+      </c>
+      <c r="E225" s="3">
+        <v>25</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>17</v>
@@ -10082,13 +10494,13 @@
         <v>420</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>186</v>
+        <v>332</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>82</v>
+        <v>112</v>
+      </c>
+      <c r="E226" s="3">
+        <v>18</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>17</v>
@@ -10103,13 +10515,13 @@
         <v>420</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>186</v>
+        <v>332</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>18</v>
+        <v>114</v>
+      </c>
+      <c r="E227" s="3">
+        <v>25</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>17</v>
@@ -10124,13 +10536,13 @@
         <v>420</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>186</v>
+        <v>332</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>193</v>
+        <v>115</v>
+      </c>
+      <c r="E228" s="3">
+        <v>25</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>17</v>
@@ -10145,13 +10557,13 @@
         <v>420</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>391</v>
+        <v>112</v>
+      </c>
+      <c r="E229" s="3">
+        <v>18</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>17</v>
@@ -10166,13 +10578,13 @@
         <v>420</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>305</v>
+        <v>114</v>
+      </c>
+      <c r="E230" s="3">
+        <v>25</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>17</v>
@@ -10187,12 +10599,14 @@
         <v>420</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E231" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="E231" s="3">
+        <v>25</v>
+      </c>
       <c r="F231" s="3" t="s">
         <v>17</v>
       </c>
@@ -10206,13 +10620,13 @@
         <v>420</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>186</v>
+        <v>334</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E232" s="3" t="s">
-        <v>308</v>
+        <v>112</v>
+      </c>
+      <c r="E232" s="3">
+        <v>18</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>17</v>
@@ -10227,12 +10641,14 @@
         <v>420</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>186</v>
+        <v>334</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E233" s="3"/>
+        <v>114</v>
+      </c>
+      <c r="E233" s="3">
+        <v>25</v>
+      </c>
       <c r="F233" s="3" t="s">
         <v>17</v>
       </c>
@@ -10243,16 +10659,16 @@
         <v>420</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>186</v>
+        <v>334</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E234" s="3" t="s">
-        <v>17</v>
+        <v>115</v>
+      </c>
+      <c r="E234" s="3">
+        <v>26</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>17</v>
@@ -10267,10 +10683,10 @@
         <v>420</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>186</v>
+        <v>466</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>273</v>
+        <v>467</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>17</v>
@@ -10288,13 +10704,13 @@
         <v>420</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>186</v>
+        <v>466</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>298</v>
+        <v>468</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>392</v>
+        <v>474</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>17</v>
@@ -10309,13 +10725,13 @@
         <v>420</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>186</v>
+        <v>466</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>299</v>
+        <v>469</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>392</v>
+        <v>475</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>17</v>
@@ -10330,13 +10746,13 @@
         <v>420</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>186</v>
+        <v>466</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>300</v>
+        <v>470</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>392</v>
+        <v>476</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>17</v>
@@ -10351,13 +10767,13 @@
         <v>420</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>186</v>
+        <v>466</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>392</v>
+        <v>57</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>17</v>
@@ -10372,13 +10788,13 @@
         <v>420</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>186</v>
+        <v>466</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>302</v>
+        <v>472</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>392</v>
+        <v>57</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>17</v>
@@ -10393,13 +10809,13 @@
         <v>420</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>186</v>
+        <v>466</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>303</v>
+        <v>473</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>17</v>
@@ -10414,13 +10830,13 @@
         <v>420</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>186</v>
+        <v>466</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>17</v>
@@ -10438,10 +10854,10 @@
         <v>186</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>310</v>
+        <v>389</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>17</v>
@@ -10459,10 +10875,10 @@
         <v>186</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>311</v>
+        <v>189</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>203</v>
+        <v>390</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>17</v>
@@ -10477,13 +10893,13 @@
         <v>420</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>396</v>
+        <v>186</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>355</v>
+        <v>181</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>393</v>
+        <v>17</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>17</v>
@@ -10498,13 +10914,13 @@
         <v>420</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>397</v>
+        <v>186</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>355</v>
+        <v>190</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>17</v>
@@ -10519,13 +10935,13 @@
         <v>420</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>398</v>
+        <v>186</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>355</v>
+        <v>191</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>393</v>
+        <v>18</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>17</v>
@@ -10540,13 +10956,13 @@
         <v>420</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>399</v>
+        <v>186</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>355</v>
+        <v>192</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>393</v>
+        <v>193</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>17</v>
@@ -10561,13 +10977,13 @@
         <v>420</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>400</v>
+        <v>186</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>17</v>
@@ -10582,13 +10998,13 @@
         <v>420</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>401</v>
+        <v>186</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>355</v>
+        <v>66</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>393</v>
+        <v>305</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>17</v>
@@ -10603,14 +11019,12 @@
         <v>420</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>402</v>
+        <v>186</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E251" s="3" t="s">
-        <v>393</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="E251" s="3"/>
       <c r="F251" s="3" t="s">
         <v>17</v>
       </c>
@@ -10624,13 +11038,13 @@
         <v>420</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>403</v>
+        <v>186</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>393</v>
+        <v>308</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>17</v>
@@ -10645,14 +11059,12 @@
         <v>420</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>404</v>
+        <v>186</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E253" s="3" t="s">
-        <v>393</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="E253" s="3"/>
       <c r="F253" s="3" t="s">
         <v>17</v>
       </c>
@@ -10663,16 +11075,16 @@
         <v>420</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>405</v>
+        <v>186</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>393</v>
+        <v>17</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>17</v>
@@ -10687,13 +11099,13 @@
         <v>420</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>406</v>
+        <v>186</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>393</v>
+        <v>17</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>17</v>
@@ -10708,13 +11120,13 @@
         <v>420</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>407</v>
+        <v>186</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>355</v>
+        <v>500</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>393</v>
+        <v>501</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>17</v>
@@ -10729,13 +11141,13 @@
         <v>420</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>408</v>
+        <v>186</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>355</v>
+        <v>502</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>393</v>
+        <v>305</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>17</v>
@@ -10750,13 +11162,13 @@
         <v>420</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>409</v>
+        <v>186</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>355</v>
+        <v>298</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>17</v>
@@ -10771,13 +11183,13 @@
         <v>420</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>410</v>
+        <v>186</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>355</v>
+        <v>299</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>17</v>
@@ -10792,13 +11204,13 @@
         <v>420</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>411</v>
+        <v>186</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>355</v>
+        <v>300</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>17</v>
@@ -10813,13 +11225,13 @@
         <v>420</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>412</v>
+        <v>186</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>355</v>
+        <v>301</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>17</v>
@@ -10834,13 +11246,13 @@
         <v>420</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>413</v>
+        <v>186</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>355</v>
+        <v>302</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>17</v>
@@ -10855,13 +11267,13 @@
         <v>420</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>414</v>
+        <v>186</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>17</v>
@@ -10876,13 +11288,13 @@
         <v>420</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>415</v>
+        <v>186</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>355</v>
+        <v>270</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>393</v>
+        <v>271</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>17</v>
@@ -10897,13 +11309,13 @@
         <v>420</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>416</v>
+        <v>186</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>355</v>
+        <v>187</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>393</v>
+        <v>310</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>17</v>
@@ -10918,13 +11330,13 @@
         <v>420</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>417</v>
+        <v>186</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>393</v>
+        <v>203</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>17</v>
@@ -10939,7 +11351,7 @@
         <v>420</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>355</v>
@@ -10953,49 +11365,595 @@
       <c r="G267" s="3"/>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A268" s="10" t="s">
+      <c r="A268" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G268" s="3"/>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A269" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G269" s="3"/>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A270" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G270" s="3"/>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A271" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G271" s="3"/>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A272" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G272" s="3"/>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A273" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G273" s="3"/>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G274" s="3"/>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A275" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G275" s="3"/>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A276" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G276" s="3"/>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A277" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G277" s="3"/>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A278" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G278" s="3"/>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A279" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G279" s="3"/>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A280" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G280" s="3"/>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A281" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G281" s="3"/>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A282" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G282" s="3"/>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A283" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G283" s="3"/>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A284" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G284" s="3"/>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A285" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G285" s="3"/>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A286" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E286" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G286" s="3"/>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A287" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G287" s="3"/>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A288" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G288" s="3"/>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A289" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G289" s="3"/>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A290" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E290" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G290" s="3"/>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A291" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G291" s="3"/>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A292" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G292" s="3"/>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A293" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G293" s="3"/>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A294" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="B268" s="10" t="s">
+      <c r="B294" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="C268" s="10" t="s">
+      <c r="C294" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="D268" s="10" t="s">
+      <c r="D294" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="E268" s="10" t="s">
+      <c r="E294" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="F268" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G268" s="10"/>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A269" s="10" t="s">
+      <c r="F294" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G294" s="10"/>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A295" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="B269" s="10" t="s">
+      <c r="B295" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="C269" s="10" t="s">
+      <c r="C295" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D269" s="10" t="s">
+      <c r="D295" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="E269" s="10" t="s">
+      <c r="E295" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="F269" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G269" s="10"/>
+      <c r="F295" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G295" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F267" xr:uid="{04129BFA-1C57-4A9F-9E8B-6ECAA0BFBBBF}"/>
+  <autoFilter ref="A1:F293" xr:uid="{04129BFA-1C57-4A9F-9E8B-6ECAA0BFBBBF}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/app/nsa_sa/DB.xlsx
+++ b/app/nsa_sa/DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aj_mac/Documents/Atel/server/code/app/nsa_sa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6B1280-0E7C-DD44-AF76-64D442A98EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D3D7D8-E8B3-1E47-8B96-F2405D969E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="620" windowWidth="14400" windowHeight="16120" firstSheet="1" activeTab="5" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15920" firstSheet="1" activeTab="5" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
   </bookViews>
   <sheets>
     <sheet name="TermPointToAmf" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="505">
   <si>
     <t>5qi1</t>
   </si>
@@ -4930,8 +4930,8 @@
       <c r="N10" s="4">
         <v>25</v>
       </c>
-      <c r="O10" s="4" t="s">
-        <v>138</v>
+      <c r="O10" s="4">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -10668,7 +10668,7 @@
         <v>115</v>
       </c>
       <c r="E234" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>17</v>

--- a/app/nsa_sa/DB.xlsx
+++ b/app/nsa_sa/DB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aj_mac/Documents/Atel/server/code/app/nsa_sa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aj_mac/Documents/Atel/server_new/app/nsa_sa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCFC4D4-098C-974E-8EB9-77AA6D2B9B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527E5214-0A7E-CA4A-92DF-9B62147E95F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16080" firstSheet="1" activeTab="5" xr2:uid="{0D659C63-0EA7-475F-99B7-E7E648DB9099}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="MOC" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MOC!$A$1:$G$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MOC!$A$1:$G$318</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2923" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2931" uniqueCount="538">
   <si>
     <t>5qi1</t>
   </si>
@@ -1650,6 +1650,12 @@
   </si>
   <si>
     <t>{"mappingInfoSIB24": "MAPPED_SI_1"}</t>
+  </si>
+  <si>
+    <t>zzzTemporary1</t>
+  </si>
+  <si>
+    <t>ENodeBFunction=1,UePolicyOptimization=1</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +1698,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1729,6 +1735,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1757,7 +1769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1771,6 +1783,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5813,7 +5826,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04129BFA-1C57-4A9F-9E8B-6ECAA0BFBBBF}">
-  <dimension ref="A1:H317"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -6009,172 +6022,174 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="A8" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="3"/>
+      <c r="G8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="3"/>
+      <c r="A9" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="3"/>
+      <c r="A10" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="11"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="3"/>
+      <c r="A11" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="3"/>
+      <c r="A12" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="11"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="3"/>
+      <c r="A13" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="11"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="3"/>
+      <c r="A14" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="11"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -6187,7 +6202,7 @@
         <v>506</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>355</v>
@@ -6211,7 +6226,7 @@
         <v>506</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>355</v>
@@ -6235,7 +6250,7 @@
         <v>506</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>355</v>
@@ -6259,7 +6274,7 @@
         <v>506</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>355</v>
@@ -6283,7 +6298,7 @@
         <v>506</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>355</v>
@@ -6307,7 +6322,7 @@
         <v>506</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>355</v>
@@ -6331,7 +6346,7 @@
         <v>506</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>355</v>
@@ -6355,7 +6370,7 @@
         <v>506</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>355</v>
@@ -6379,7 +6394,7 @@
         <v>506</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>355</v>
@@ -6403,7 +6418,7 @@
         <v>506</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>355</v>
@@ -6427,7 +6442,7 @@
         <v>506</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>355</v>
@@ -6451,7 +6466,7 @@
         <v>506</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>355</v>
@@ -6475,7 +6490,7 @@
         <v>506</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>355</v>
@@ -6499,7 +6514,7 @@
         <v>506</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>355</v>
@@ -6523,7 +6538,7 @@
         <v>506</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>355</v>
@@ -6547,7 +6562,7 @@
         <v>506</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>494</v>
+        <v>411</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>355</v>
@@ -6571,7 +6586,7 @@
         <v>506</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>495</v>
+        <v>412</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>355</v>
@@ -6595,7 +6610,7 @@
         <v>506</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>496</v>
+        <v>413</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>355</v>
@@ -6619,7 +6634,7 @@
         <v>506</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>497</v>
+        <v>414</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>355</v>
@@ -6643,7 +6658,7 @@
         <v>506</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>498</v>
+        <v>415</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>355</v>
@@ -6667,13 +6682,13 @@
         <v>506</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>164</v>
+        <v>416</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>165</v>
+        <v>355</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>168</v>
+        <v>393</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>17</v>
@@ -6691,13 +6706,13 @@
         <v>506</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>164</v>
+        <v>417</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>166</v>
+        <v>355</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>17</v>
+        <v>393</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>17</v>
@@ -6715,13 +6730,13 @@
         <v>506</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>167</v>
+        <v>495</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>165</v>
+        <v>355</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>168</v>
+        <v>393</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>17</v>
@@ -6739,13 +6754,13 @@
         <v>506</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>167</v>
+        <v>496</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>166</v>
+        <v>355</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>17</v>
+        <v>393</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>17</v>
@@ -6763,13 +6778,13 @@
         <v>506</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>313</v>
+        <v>497</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>17</v>
+        <v>393</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>17</v>
@@ -6787,13 +6802,13 @@
         <v>506</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>315</v>
+        <v>498</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>17</v>
@@ -6811,13 +6826,13 @@
         <v>506</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>315</v>
+        <v>164</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>317</v>
+        <v>165</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>17</v>
@@ -6835,13 +6850,13 @@
         <v>506</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>315</v>
+        <v>164</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>318</v>
+        <v>166</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>17</v>
@@ -6859,13 +6874,13 @@
         <v>506</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>315</v>
+        <v>167</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>319</v>
+        <v>165</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>17</v>
@@ -6883,13 +6898,13 @@
         <v>506</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>315</v>
+        <v>167</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>320</v>
+        <v>166</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -6907,13 +6922,13 @@
         <v>506</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" s="3">
-        <v>34</v>
+        <v>314</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -6931,13 +6946,13 @@
         <v>506</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F46" s="3">
-        <v>34</v>
+        <v>316</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -6955,13 +6970,13 @@
         <v>506</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F47" s="3">
-        <v>12</v>
+        <v>317</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -6979,13 +6994,13 @@
         <v>506</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F48" s="3">
-        <v>12</v>
+        <v>318</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -7003,13 +7018,13 @@
         <v>506</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F49" s="3">
-        <v>46</v>
+        <v>319</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -7027,13 +7042,13 @@
         <v>506</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F50" s="3">
-        <v>32</v>
+        <v>320</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -7051,13 +7066,13 @@
         <v>506</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F51" s="3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -7075,13 +7090,13 @@
         <v>506</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F52" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -7099,13 +7114,13 @@
         <v>506</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F53" s="3">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>17</v>
@@ -7123,13 +7138,13 @@
         <v>506</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>139</v>
+        <v>341</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>158</v>
+        <v>93</v>
+      </c>
+      <c r="F54" s="3">
+        <v>12</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>17</v>
@@ -7147,13 +7162,13 @@
         <v>506</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>139</v>
+        <v>342</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>158</v>
+        <v>93</v>
+      </c>
+      <c r="F55" s="3">
+        <v>46</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>17</v>
@@ -7171,13 +7186,13 @@
         <v>506</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>139</v>
+        <v>343</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>123</v>
+        <v>93</v>
+      </c>
+      <c r="F56" s="3">
+        <v>32</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>17</v>
@@ -7195,13 +7210,13 @@
         <v>506</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>139</v>
+        <v>344</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>58</v>
+        <v>93</v>
+      </c>
+      <c r="F57" s="3">
+        <v>40</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>17</v>
@@ -7219,13 +7234,13 @@
         <v>506</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>139</v>
+        <v>345</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>17</v>
+        <v>93</v>
+      </c>
+      <c r="F58" s="3">
+        <v>30</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -7243,13 +7258,13 @@
         <v>506</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>139</v>
+        <v>346</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>380</v>
+        <v>93</v>
+      </c>
+      <c r="F59" s="3">
+        <v>26</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -7267,13 +7282,13 @@
         <v>506</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>17</v>
@@ -7291,13 +7306,13 @@
         <v>506</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>17</v>
@@ -7315,10 +7330,10 @@
         <v>506</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>123</v>
@@ -7339,13 +7354,13 @@
         <v>506</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>17</v>
@@ -7363,10 +7378,10 @@
         <v>506</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>17</v>
@@ -7387,13 +7402,13 @@
         <v>506</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>17</v>
@@ -7411,13 +7426,13 @@
         <v>506</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>17</v>
@@ -7435,13 +7450,13 @@
         <v>506</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>17</v>
+        <v>163</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>17</v>
@@ -7459,13 +7474,13 @@
         <v>506</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>17</v>
@@ -7483,13 +7498,13 @@
         <v>506</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>17</v>
@@ -7507,13 +7522,13 @@
         <v>506</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>232</v>
+        <v>153</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>17</v>
@@ -7531,13 +7546,13 @@
         <v>506</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>232</v>
+        <v>153</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>297</v>
+        <v>155</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>17</v>
+        <v>381</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>17</v>
@@ -7555,13 +7570,13 @@
         <v>506</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>233</v>
+        <v>153</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>17</v>
@@ -7579,13 +7594,13 @@
         <v>506</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>476</v>
+        <v>153</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>234</v>
+        <v>157</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>477</v>
+        <v>17</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>17</v>
@@ -7603,13 +7618,13 @@
         <v>506</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>476</v>
+        <v>149</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>478</v>
+        <v>150</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>17</v>
@@ -7627,13 +7642,13 @@
         <v>506</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>476</v>
+        <v>151</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>479</v>
+        <v>152</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>17</v>
@@ -7651,13 +7666,13 @@
         <v>506</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>476</v>
+        <v>232</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>269</v>
+        <v>85</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>255</v>
+        <v>72</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>17</v>
@@ -7675,10 +7690,10 @@
         <v>506</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>17</v>
@@ -7699,13 +7714,13 @@
         <v>506</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>17</v>
@@ -7723,13 +7738,13 @@
         <v>506</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>235</v>
+        <v>476</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>382</v>
+        <v>477</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>17</v>
@@ -7747,13 +7762,13 @@
         <v>506</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>235</v>
+        <v>476</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>237</v>
+        <v>478</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>238</v>
+        <v>123</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>17</v>
@@ -7771,13 +7786,13 @@
         <v>506</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>235</v>
+        <v>476</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>239</v>
+        <v>479</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>383</v>
+        <v>123</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>17</v>
@@ -7795,13 +7810,13 @@
         <v>506</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>235</v>
+        <v>476</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>383</v>
+        <v>255</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>17</v>
@@ -7819,13 +7834,13 @@
         <v>506</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>17</v>
@@ -7843,13 +7858,13 @@
         <v>506</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>384</v>
+        <v>17</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>17</v>
@@ -7870,10 +7885,10 @@
         <v>235</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>244</v>
+        <v>382</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>17</v>
@@ -7894,10 +7909,10 @@
         <v>235</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>17</v>
@@ -7915,13 +7930,13 @@
         <v>506</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>120</v>
+        <v>239</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>17</v>
+        <v>383</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>17</v>
@@ -7939,13 +7954,13 @@
         <v>506</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>121</v>
+        <v>240</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>56</v>
+        <v>383</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>17</v>
@@ -7963,13 +7978,13 @@
         <v>506</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>17</v>
@@ -7987,13 +8002,13 @@
         <v>506</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>124</v>
+        <v>235</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>72</v>
+        <v>384</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>17</v>
@@ -8011,13 +8026,13 @@
         <v>506</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>126</v>
+        <v>235</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>127</v>
+        <v>243</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>17</v>
@@ -8035,13 +8050,13 @@
         <v>506</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>126</v>
+        <v>235</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>128</v>
+        <v>245</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>395</v>
+        <v>246</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>17</v>
@@ -8059,13 +8074,13 @@
         <v>506</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>253</v>
+        <v>119</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>254</v>
+        <v>120</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>255</v>
+        <v>17</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>17</v>
@@ -8083,13 +8098,13 @@
         <v>506</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>275</v>
+        <v>119</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>276</v>
+        <v>121</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>255</v>
+        <v>56</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>17</v>
@@ -8107,13 +8122,13 @@
         <v>506</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>275</v>
+        <v>119</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>277</v>
+        <v>122</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>17</v>
@@ -8131,12 +8146,14 @@
         <v>506</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>252</v>
+        <v>124</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F96" s="3"/>
+        <v>125</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="G96" s="3" t="s">
         <v>17</v>
       </c>
@@ -8153,13 +8170,13 @@
         <v>506</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>295</v>
+        <v>126</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>280</v>
+        <v>127</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>384</v>
+        <v>16</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>17</v>
@@ -8177,13 +8194,13 @@
         <v>506</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>295</v>
+        <v>126</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>281</v>
+        <v>128</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>17</v>
+        <v>395</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>17</v>
@@ -8201,13 +8218,13 @@
         <v>506</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>73</v>
+        <v>255</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>17</v>
@@ -8225,13 +8242,13 @@
         <v>506</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>17</v>
@@ -8249,13 +8266,13 @@
         <v>506</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>421</v>
+        <v>255</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>17</v>
@@ -8273,14 +8290,12 @@
         <v>506</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>295</v>
+        <v>252</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>290</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>17</v>
       </c>
@@ -8300,10 +8315,10 @@
         <v>295</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>291</v>
+        <v>384</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>17</v>
@@ -8321,13 +8336,13 @@
         <v>506</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>384</v>
+        <v>17</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>17</v>
@@ -8345,13 +8360,13 @@
         <v>506</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>17</v>
@@ -8369,13 +8384,13 @@
         <v>506</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>17</v>
@@ -8393,13 +8408,13 @@
         <v>506</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>283</v>
+        <v>421</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>17</v>
@@ -8417,13 +8432,13 @@
         <v>506</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>17</v>
@@ -8441,13 +8456,13 @@
         <v>506</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>17</v>
@@ -8468,10 +8483,10 @@
         <v>296</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>292</v>
+        <v>384</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>17</v>
@@ -8492,10 +8507,10 @@
         <v>296</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>293</v>
+        <v>18</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>17</v>
@@ -8516,10 +8531,10 @@
         <v>296</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>294</v>
+        <v>73</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>17</v>
@@ -8537,13 +8552,13 @@
         <v>506</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>322</v>
+        <v>268</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>16</v>
+        <v>283</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>17</v>
@@ -8561,13 +8576,13 @@
         <v>506</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>323</v>
+        <v>269</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>158</v>
+        <v>255</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>17</v>
@@ -8585,13 +8600,13 @@
         <v>506</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>17</v>
+        <v>286</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>17</v>
@@ -8609,13 +8624,13 @@
         <v>506</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>17</v>
@@ -8633,13 +8648,13 @@
         <v>506</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>325</v>
+        <v>293</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>17</v>
@@ -8657,13 +8672,13 @@
         <v>506</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>16</v>
+        <v>294</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>17</v>
@@ -8681,13 +8696,13 @@
         <v>506</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>17</v>
@@ -8705,13 +8720,13 @@
         <v>506</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>17</v>
@@ -8729,13 +8744,13 @@
         <v>506</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>327</v>
+        <v>17</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>17</v>
@@ -8753,13 +8768,13 @@
         <v>506</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>17</v>
@@ -8777,13 +8792,13 @@
         <v>506</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>16</v>
+        <v>325</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>17</v>
@@ -8801,13 +8816,13 @@
         <v>506</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>17</v>
@@ -8825,13 +8840,13 @@
         <v>506</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>17</v>
@@ -8849,13 +8864,13 @@
         <v>506</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>329</v>
+        <v>18</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>17</v>
@@ -8873,13 +8888,13 @@
         <v>506</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>17</v>
@@ -8897,13 +8912,13 @@
         <v>506</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>454</v>
+        <v>326</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>455</v>
+        <v>269</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>456</v>
+        <v>327</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>17</v>
@@ -8921,13 +8936,13 @@
         <v>506</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>457</v>
+        <v>328</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>455</v>
+        <v>322</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>456</v>
+        <v>16</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>17</v>
@@ -8945,13 +8960,13 @@
         <v>506</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>419</v>
+        <v>328</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>17</v>
@@ -8969,13 +8984,13 @@
         <v>506</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>419</v>
+        <v>328</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>350</v>
+        <v>17</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>17</v>
@@ -8993,13 +9008,13 @@
         <v>506</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>348</v>
+        <v>268</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>18</v>
+        <v>329</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>17</v>
@@ -9017,13 +9032,13 @@
         <v>506</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>349</v>
+        <v>269</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>17</v>
@@ -9041,13 +9056,13 @@
         <v>506</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>351</v>
+        <v>454</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>348</v>
+        <v>455</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>17</v>
+        <v>456</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>17</v>
@@ -9065,13 +9080,13 @@
         <v>506</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>351</v>
+        <v>457</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>349</v>
+        <v>455</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>350</v>
+        <v>456</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>17</v>
@@ -9089,13 +9104,13 @@
         <v>506</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>502</v>
+        <v>419</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F136" s="3">
-        <v>20</v>
+        <v>348</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>17</v>
@@ -9113,13 +9128,13 @@
         <v>506</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>503</v>
+        <v>419</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F137" s="3">
-        <v>200</v>
+        <v>349</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>17</v>
@@ -9137,13 +9152,13 @@
         <v>506</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>221</v>
+        <v>347</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>228</v>
+        <v>348</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>17</v>
@@ -9161,13 +9176,13 @@
         <v>506</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>221</v>
+        <v>347</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>57</v>
+        <v>350</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>17</v>
@@ -9185,12 +9200,14 @@
         <v>506</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F140" s="3"/>
+        <v>348</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="G140" s="3" t="s">
         <v>17</v>
       </c>
@@ -9207,13 +9224,13 @@
         <v>506</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>230</v>
+        <v>349</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>39</v>
+        <v>350</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>17</v>
@@ -9231,13 +9248,13 @@
         <v>506</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>221</v>
+        <v>502</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>39</v>
+        <v>107</v>
+      </c>
+      <c r="F142" s="3">
+        <v>20</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>17</v>
@@ -9255,13 +9272,13 @@
         <v>506</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>221</v>
+        <v>503</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>250</v>
+        <v>107</v>
+      </c>
+      <c r="F143" s="3">
+        <v>200</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>17</v>
@@ -9282,10 +9299,10 @@
         <v>221</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>251</v>
+        <v>17</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>17</v>
@@ -9306,10 +9323,10 @@
         <v>221</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>252</v>
+        <v>57</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>17</v>
@@ -9327,14 +9344,12 @@
         <v>506</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>178</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
         <v>17</v>
       </c>
@@ -9351,13 +9366,13 @@
         <v>506</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>394</v>
+        <v>39</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>17</v>
@@ -9375,13 +9390,13 @@
         <v>506</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>17</v>
@@ -9399,13 +9414,13 @@
         <v>506</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>17</v>
@@ -9423,13 +9438,13 @@
         <v>506</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>168</v>
+        <v>251</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>17</v>
@@ -9447,13 +9462,13 @@
         <v>506</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>168</v>
+        <v>252</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>17</v>
@@ -9471,13 +9486,13 @@
         <v>506</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>17</v>
@@ -9495,13 +9510,13 @@
         <v>506</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>179</v>
+        <v>394</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>17</v>
@@ -9519,13 +9534,13 @@
         <v>506</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F154" s="3">
-        <v>1500</v>
+        <v>172</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>17</v>
@@ -9543,13 +9558,13 @@
         <v>506</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F155" s="3">
-        <v>600</v>
+        <v>173</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>17</v>
@@ -9567,13 +9582,13 @@
         <v>506</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F156" s="3">
-        <v>2000</v>
+        <v>175</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>17</v>
@@ -9591,13 +9606,13 @@
         <v>506</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F157" s="3">
-        <v>3000</v>
+        <v>177</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>17</v>
@@ -9615,13 +9630,13 @@
         <v>506</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F158" s="3">
-        <v>400</v>
+        <v>176</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>17</v>
@@ -9639,13 +9654,13 @@
         <v>506</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>17</v>
+        <v>179</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>17</v>
@@ -9663,13 +9678,13 @@
         <v>506</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>385</v>
+        <v>130</v>
+      </c>
+      <c r="F160" s="3">
+        <v>1500</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>17</v>
@@ -9687,13 +9702,13 @@
         <v>506</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>356</v>
+        <v>129</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>255</v>
+        <v>131</v>
+      </c>
+      <c r="F161" s="3">
+        <v>600</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>17</v>
@@ -9711,13 +9726,13 @@
         <v>506</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>356</v>
+        <v>129</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>363</v>
+        <v>132</v>
+      </c>
+      <c r="F162" s="3">
+        <v>2000</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>17</v>
@@ -9735,13 +9750,13 @@
         <v>506</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>356</v>
+        <v>129</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>362</v>
+        <v>133</v>
+      </c>
+      <c r="F163" s="3">
+        <v>3000</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>17</v>
@@ -9759,13 +9774,13 @@
         <v>506</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>356</v>
+        <v>129</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>361</v>
+        <v>134</v>
+      </c>
+      <c r="F164" s="3">
+        <v>400</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>17</v>
@@ -9783,13 +9798,13 @@
         <v>506</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>356</v>
+        <v>180</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>359</v>
+        <v>181</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>360</v>
+        <v>17</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>17</v>
@@ -9807,13 +9822,13 @@
         <v>506</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G166" s="3" t="s">
         <v>17</v>
@@ -9831,13 +9846,13 @@
         <v>506</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>199</v>
+        <v>356</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>197</v>
+        <v>268</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>17</v>
@@ -9855,13 +9870,13 @@
         <v>506</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>199</v>
+        <v>356</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>196</v>
+        <v>269</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>17</v>
+        <v>363</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>17</v>
@@ -9879,13 +9894,13 @@
         <v>506</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>200</v>
+        <v>356</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>195</v>
+        <v>357</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>17</v>
@@ -9903,13 +9918,13 @@
         <v>506</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>200</v>
+        <v>356</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>197</v>
+        <v>358</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>217</v>
+        <v>361</v>
       </c>
       <c r="G170" s="3" t="s">
         <v>17</v>
@@ -9927,13 +9942,13 @@
         <v>506</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>200</v>
+        <v>356</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>196</v>
+        <v>359</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>17</v>
+        <v>360</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>17</v>
@@ -9951,7 +9966,7 @@
         <v>506</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>195</v>
@@ -9975,13 +9990,13 @@
         <v>506</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>196</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>17</v>
@@ -9999,13 +10014,13 @@
         <v>506</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>217</v>
+        <v>386</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>17</v>
@@ -10023,13 +10038,13 @@
         <v>506</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>386</v>
+        <v>17</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>17</v>
@@ -10047,13 +10062,13 @@
         <v>506</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>18</v>
+        <v>387</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>17</v>
@@ -10071,13 +10086,13 @@
         <v>506</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>17</v>
@@ -10095,13 +10110,13 @@
         <v>506</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>195</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>17</v>
@@ -10119,7 +10134,7 @@
         <v>506</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>196</v>
@@ -10146,10 +10161,10 @@
         <v>201</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>217</v>
+        <v>387</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>17</v>
@@ -10167,13 +10182,13 @@
         <v>506</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>386</v>
+        <v>18</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>17</v>
@@ -10194,10 +10209,10 @@
         <v>202</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>18</v>
+        <v>386</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>17</v>
@@ -10218,10 +10233,10 @@
         <v>202</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>17</v>
@@ -12923,13 +12938,13 @@
         <v>505</v>
       </c>
       <c r="D296" s="9" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="E296" s="9" t="s">
-        <v>508</v>
+        <v>536</v>
       </c>
       <c r="F296" s="9" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G296" s="9" t="s">
         <v>17</v>
@@ -12950,10 +12965,10 @@
         <v>507</v>
       </c>
       <c r="E297" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F297" s="9" t="s">
-        <v>535</v>
+        <v>18</v>
       </c>
       <c r="G297" s="9" t="s">
         <v>17</v>
@@ -12974,10 +12989,10 @@
         <v>507</v>
       </c>
       <c r="E298" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F298" s="9" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="G298" s="9" t="s">
         <v>17</v>
@@ -12995,13 +13010,13 @@
         <v>505</v>
       </c>
       <c r="D299" s="9" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="E299" s="9" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F299" s="9" t="s">
-        <v>18</v>
+        <v>511</v>
       </c>
       <c r="G299" s="9" t="s">
         <v>17</v>
@@ -13022,10 +13037,10 @@
         <v>513</v>
       </c>
       <c r="E300" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F300" s="9" t="s">
-        <v>535</v>
+        <v>18</v>
       </c>
       <c r="G300" s="9" t="s">
         <v>17</v>
@@ -13046,10 +13061,10 @@
         <v>513</v>
       </c>
       <c r="E301" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F301" s="9" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="G301" s="9" t="s">
         <v>17</v>
@@ -13067,13 +13082,13 @@
         <v>505</v>
       </c>
       <c r="D302" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E302" s="9" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F302" s="9" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G302" s="9" t="s">
         <v>17</v>
@@ -13094,7 +13109,7 @@
         <v>512</v>
       </c>
       <c r="E303" s="9" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>515</v>
@@ -13118,10 +13133,10 @@
         <v>512</v>
       </c>
       <c r="E304" s="9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F304" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G304" s="9" t="s">
         <v>17</v>
@@ -13142,10 +13157,10 @@
         <v>512</v>
       </c>
       <c r="E305" s="9" t="s">
-        <v>279</v>
+        <v>517</v>
       </c>
       <c r="F305" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G305" s="9" t="s">
         <v>17</v>
@@ -13166,10 +13181,10 @@
         <v>512</v>
       </c>
       <c r="E306" s="9" t="s">
-        <v>520</v>
+        <v>279</v>
       </c>
       <c r="F306" s="9" t="s">
-        <v>17</v>
+        <v>519</v>
       </c>
       <c r="G306" s="9" t="s">
         <v>17</v>
@@ -13190,7 +13205,7 @@
         <v>512</v>
       </c>
       <c r="E307" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>17</v>
@@ -13211,13 +13226,13 @@
         <v>505</v>
       </c>
       <c r="D308" s="9" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="E308" s="9" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F308" s="9" t="s">
-        <v>524</v>
+        <v>17</v>
       </c>
       <c r="G308" s="9" t="s">
         <v>17</v>
@@ -13238,10 +13253,10 @@
         <v>522</v>
       </c>
       <c r="E309" s="9" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F309" s="9" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G309" s="9" t="s">
         <v>17</v>
@@ -13262,10 +13277,10 @@
         <v>522</v>
       </c>
       <c r="E310" s="9" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F310" s="9" t="s">
-        <v>37</v>
+        <v>526</v>
       </c>
       <c r="G310" s="9" t="s">
         <v>17</v>
@@ -13286,10 +13301,10 @@
         <v>522</v>
       </c>
       <c r="E311" s="9" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F311" s="9" t="s">
-        <v>529</v>
+        <v>37</v>
       </c>
       <c r="G311" s="9" t="s">
         <v>17</v>
@@ -13307,13 +13322,13 @@
         <v>505</v>
       </c>
       <c r="D312" s="9" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="E312" s="9" t="s">
-        <v>42</v>
+        <v>528</v>
       </c>
       <c r="F312" s="9" t="s">
-        <v>17</v>
+        <v>529</v>
       </c>
       <c r="G312" s="9" t="s">
         <v>17</v>
@@ -13334,10 +13349,10 @@
         <v>530</v>
       </c>
       <c r="E313" s="9" t="s">
-        <v>531</v>
+        <v>42</v>
       </c>
       <c r="F313" s="9" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="G313" s="9" t="s">
         <v>17</v>
@@ -13358,7 +13373,7 @@
         <v>530</v>
       </c>
       <c r="E314" s="9" t="s">
-        <v>52</v>
+        <v>531</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>72</v>
@@ -13382,10 +13397,10 @@
         <v>530</v>
       </c>
       <c r="E315" s="9" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F315" s="9" t="s">
-        <v>305</v>
+        <v>72</v>
       </c>
       <c r="G315" s="9" t="s">
         <v>17</v>
@@ -13406,10 +13421,10 @@
         <v>530</v>
       </c>
       <c r="E316" s="9" t="s">
-        <v>532</v>
+        <v>66</v>
       </c>
       <c r="F316" s="9" t="s">
-        <v>39</v>
+        <v>305</v>
       </c>
       <c r="G316" s="9" t="s">
         <v>17</v>
@@ -13430,18 +13445,42 @@
         <v>530</v>
       </c>
       <c r="E317" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="F317" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G317" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H317" s="9"/>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A318" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B318" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C318" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="D318" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="E318" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="F317" s="9" t="s">
+      <c r="F318" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="G317" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H317" s="9"/>
+      <c r="G318" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H318" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G286" xr:uid="{04129BFA-1C57-4A9F-9E8B-6ECAA0BFBBBF}"/>
+  <autoFilter ref="A1:G318" xr:uid="{04129BFA-1C57-4A9F-9E8B-6ECAA0BFBBBF}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
